--- a/sinchi metals assays over time.xlsx
+++ b/sinchi metals assays over time.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5dd0d63cd58a577/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\claude\SMPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{110D6841-A5A1-4450-B814-C6B26FA16C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F61AF4EE-80AF-41B0-9F8E-250109D7ED1F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E0387D-6212-4C6C-A810-833A71F7D972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19890" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{786040CA-C117-4D0F-BDFA-1AE45497D150}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{786040CA-C117-4D0F-BDFA-1AE45497D150}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -1455,7 +1455,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1726,6 +1726,7 @@
     <xf numFmtId="166" fontId="8" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1825,7 +1826,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1FF62F3F-9C45-4981-80CA-DD7D85DCFAA1}" name="Table1" displayName="Table1" ref="A1:AD454" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9">
-  <autoFilter ref="A1:AD454" xr:uid="{1FF62F3F-9C45-4981-80CA-DD7D85DCFAA1}"/>
+  <autoFilter ref="A1:AD454" xr:uid="{1FF62F3F-9C45-4981-80CA-DD7D85DCFAA1}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="93302"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{7F78213E-9C1A-4957-BB0D-8340CDD31563}" name="Open/Close" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{1B46E019-1EBF-46CE-9BBA-1DC43C21DA3F}" name="P/S" dataDxfId="7"/>
@@ -2310,7 +2317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="48" t="s">
         <v>57</v>
       </c>
@@ -2379,7 +2386,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="48" t="s">
         <v>57</v>
       </c>
@@ -2440,7 +2447,7 @@
         <v>3.0599999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="48" t="s">
         <v>57</v>
       </c>
@@ -2513,7 +2520,7 @@
         <v>2.46E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="48" t="s">
         <v>57</v>
       </c>
@@ -2568,7 +2575,7 @@
       <c r="AC5" s="62"/>
       <c r="AD5" s="29"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="48" t="s">
         <v>57</v>
       </c>
@@ -2640,7 +2647,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="48" t="s">
         <v>57</v>
       </c>
@@ -2705,7 +2712,7 @@
       <c r="AB7" s="9"/>
       <c r="AC7" s="9"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="48" t="s">
         <v>57</v>
       </c>
@@ -2771,7 +2778,7 @@
       <c r="AC8" s="9"/>
       <c r="AD8" s="29"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="48" t="s">
         <v>57</v>
       </c>
@@ -2839,7 +2846,7 @@
         <v>2.2754545454545472E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="48" t="s">
         <v>57</v>
       </c>
@@ -2908,7 +2915,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="48" t="s">
         <v>57</v>
       </c>
@@ -2984,7 +2991,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="48" t="s">
         <v>57</v>
       </c>
@@ -3047,7 +3054,7 @@
       <c r="AC12" s="61"/>
       <c r="AD12" s="29"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="48" t="s">
         <v>57</v>
       </c>
@@ -3112,7 +3119,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="48" t="s">
         <v>57</v>
       </c>
@@ -3177,7 +3184,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="48" t="s">
         <v>57</v>
       </c>
@@ -3245,7 +3252,7 @@
         <v>3.6266233766233835E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="48" t="s">
         <v>57</v>
       </c>
@@ -3314,7 +3321,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="48" t="s">
         <v>57</v>
       </c>
@@ -3387,7 +3394,7 @@
         <v>2.2100000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="48" t="s">
         <v>57</v>
       </c>
@@ -3459,7 +3466,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="48" t="s">
         <v>57</v>
       </c>
@@ -3523,7 +3530,7 @@
       <c r="AE19" s="80"/>
       <c r="AF19" s="80"/>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="48" t="s">
         <v>57</v>
       </c>
@@ -3580,7 +3587,7 @@
       <c r="AE20" s="80"/>
       <c r="AF20" s="80"/>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="48" t="s">
         <v>57</v>
       </c>
@@ -3650,7 +3657,7 @@
       <c r="AE21" s="80"/>
       <c r="AF21" s="80"/>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="48" t="s">
         <v>57</v>
       </c>
@@ -3719,7 +3726,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="48" t="s">
         <v>57</v>
       </c>
@@ -3789,7 +3796,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="48" t="s">
         <v>57</v>
       </c>
@@ -3844,7 +3851,7 @@
       <c r="AC24" s="61"/>
       <c r="AD24" s="29"/>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="48" t="s">
         <v>57</v>
       </c>
@@ -3893,7 +3900,7 @@
       <c r="AC25" s="61"/>
       <c r="AD25" s="29"/>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="48" t="s">
         <v>57</v>
       </c>
@@ -3947,7 +3954,7 @@
       <c r="AC26" s="61"/>
       <c r="AD26" s="29"/>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="48" t="s">
         <v>57</v>
       </c>
@@ -4010,7 +4017,7 @@
       <c r="AC27" s="9"/>
       <c r="AD27" s="29"/>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" s="48" t="s">
         <v>57</v>
       </c>
@@ -4055,7 +4062,7 @@
       <c r="AC28" s="9"/>
       <c r="AD28" s="29"/>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="48" t="s">
         <v>57</v>
       </c>
@@ -4099,7 +4106,7 @@
       <c r="AB29" s="9"/>
       <c r="AC29" s="9"/>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="48" t="s">
         <v>57</v>
       </c>
@@ -4143,7 +4150,7 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="48" t="s">
         <v>57</v>
       </c>
@@ -4208,7 +4215,7 @@
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="48" t="s">
         <v>57</v>
       </c>
@@ -4273,7 +4280,7 @@
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="48" t="s">
         <v>57</v>
       </c>
@@ -4341,7 +4348,7 @@
         <v>1.9734848484848411E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="48" t="s">
         <v>57</v>
       </c>
@@ -4410,7 +4417,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="48" t="s">
         <v>57</v>
       </c>
@@ -4474,7 +4481,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="48" t="s">
         <v>57</v>
       </c>
@@ -4529,7 +4536,7 @@
       <c r="AC36" s="62"/>
       <c r="AD36" s="29"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="48" t="s">
         <v>57</v>
       </c>
@@ -4590,7 +4597,7 @@
       <c r="AC37" s="61"/>
       <c r="AD37" s="29"/>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" s="48" t="s">
         <v>57</v>
       </c>
@@ -4659,7 +4666,7 @@
       <c r="AC38" s="61"/>
       <c r="AD38" s="29"/>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="48" t="s">
         <v>57</v>
       </c>
@@ -4724,7 +4731,7 @@
       <c r="AC39" s="9"/>
       <c r="AD39" s="29"/>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="48" t="s">
         <v>57</v>
       </c>
@@ -4789,7 +4796,7 @@
       <c r="AC40" s="9"/>
       <c r="AD40" s="29"/>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="48" t="s">
         <v>57</v>
       </c>
@@ -4846,7 +4853,7 @@
       </c>
       <c r="AD41" s="29"/>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="48" t="s">
         <v>57</v>
       </c>
@@ -4903,7 +4910,7 @@
       </c>
       <c r="AD42" s="29"/>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="48" t="s">
         <v>57</v>
       </c>
@@ -4961,7 +4968,7 @@
       </c>
       <c r="AD43" s="21"/>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="48" t="s">
         <v>57</v>
       </c>
@@ -5005,7 +5012,7 @@
       <c r="AB44" s="9"/>
       <c r="AC44" s="9"/>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" s="48" t="s">
         <v>57</v>
       </c>
@@ -5070,7 +5077,7 @@
       <c r="AB45" s="9"/>
       <c r="AC45" s="9"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="48" t="s">
         <v>57</v>
       </c>
@@ -5125,7 +5132,7 @@
       <c r="AB46" s="9"/>
       <c r="AC46" s="9"/>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="48" t="s">
         <v>57</v>
       </c>
@@ -5197,7 +5204,7 @@
         <v>1.6590909090909101E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="48" t="s">
         <v>57</v>
       </c>
@@ -5266,7 +5273,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="48" t="s">
         <v>57</v>
       </c>
@@ -5330,7 +5337,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="48" t="s">
         <v>57</v>
       </c>
@@ -5385,7 +5392,7 @@
       <c r="AC50" s="62"/>
       <c r="AD50" s="29"/>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="48" t="s">
         <v>57</v>
       </c>
@@ -5448,7 +5455,7 @@
       <c r="AC51" s="62"/>
       <c r="AD51" s="29"/>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="48" t="s">
         <v>57</v>
       </c>
@@ -5513,7 +5520,7 @@
       </c>
       <c r="AD52" s="29"/>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" s="48" t="s">
         <v>57</v>
       </c>
@@ -5578,7 +5585,7 @@
       </c>
       <c r="AD53" s="29"/>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="48" t="s">
         <v>57</v>
       </c>
@@ -5664,7 +5671,7 @@
       </c>
       <c r="AD54" s="91"/>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" s="48" t="s">
         <v>57</v>
       </c>
@@ -5731,7 +5738,7 @@
       <c r="AC55" s="62"/>
       <c r="AD55" s="29"/>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" s="48" t="s">
         <v>57</v>
       </c>
@@ -5794,7 +5801,7 @@
       <c r="AC56" s="62"/>
       <c r="AD56" s="29"/>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="48" t="s">
         <v>57</v>
       </c>
@@ -5851,7 +5858,7 @@
       </c>
       <c r="AD57" s="29"/>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="48" t="s">
         <v>57</v>
       </c>
@@ -5908,7 +5915,7 @@
       </c>
       <c r="AD58" s="29"/>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" s="48" t="s">
         <v>57</v>
       </c>
@@ -5968,7 +5975,7 @@
       </c>
       <c r="AD59" s="21"/>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" s="48" t="s">
         <v>57</v>
       </c>
@@ -6033,7 +6040,7 @@
       <c r="AB60" s="9"/>
       <c r="AC60" s="9"/>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" s="48" t="s">
         <v>57</v>
       </c>
@@ -6088,7 +6095,7 @@
       <c r="AB61" s="9"/>
       <c r="AC61" s="9"/>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" s="48" t="s">
         <v>57</v>
       </c>
@@ -6172,7 +6179,7 @@
         <v>1.6405303030303076E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" s="48" t="s">
         <v>57</v>
       </c>
@@ -6241,7 +6248,7 @@
         <v>1.01E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" s="48" t="s">
         <v>57</v>
       </c>
@@ -6313,7 +6320,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" s="48" t="s">
         <v>57</v>
       </c>
@@ -6380,7 +6387,7 @@
       <c r="AC65" s="61"/>
       <c r="AD65" s="29"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="48" t="s">
         <v>57</v>
       </c>
@@ -6436,7 +6443,7 @@
       </c>
       <c r="AD66" s="29"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="48" t="s">
         <v>57</v>
       </c>
@@ -6492,7 +6499,7 @@
       </c>
       <c r="AD67" s="29"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="48" t="s">
         <v>57</v>
       </c>
@@ -6550,7 +6557,7 @@
       </c>
       <c r="AD68" s="91"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="48" t="s">
         <v>57</v>
       </c>
@@ -6613,7 +6620,7 @@
       <c r="AC69" s="9"/>
       <c r="AD69" s="29"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" s="48" t="s">
         <v>57</v>
       </c>
@@ -6657,7 +6664,7 @@
       <c r="AB70" s="9"/>
       <c r="AC70" s="9"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" s="48" t="s">
         <v>57</v>
       </c>
@@ -6701,7 +6708,7 @@
       <c r="AB71" s="9"/>
       <c r="AC71" s="9"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" s="48" t="s">
         <v>57</v>
       </c>
@@ -6760,7 +6767,7 @@
         <v>152.27699999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" s="48" t="s">
         <v>57</v>
       </c>
@@ -6817,7 +6824,7 @@
       <c r="AB73" s="9"/>
       <c r="AC73" s="9"/>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="48" t="s">
         <v>57</v>
       </c>
@@ -6876,7 +6883,7 @@
         <v>152.32499999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" s="48" t="s">
         <v>57</v>
       </c>
@@ -6933,7 +6940,7 @@
       <c r="AB75" s="9"/>
       <c r="AC75" s="9"/>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" s="48" t="s">
         <v>57</v>
       </c>
@@ -6990,7 +6997,7 @@
       <c r="AB76" s="20"/>
       <c r="AC76" s="20"/>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" s="48" t="s">
         <v>57</v>
       </c>
@@ -7049,7 +7056,7 @@
         <v>304.60199999999998</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="48" t="s">
         <v>57</v>
       </c>
@@ -7106,7 +7113,7 @@
       <c r="AB78" s="9"/>
       <c r="AC78" s="9"/>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="48" t="s">
         <v>57</v>
       </c>
@@ -7149,7 +7156,7 @@
       <c r="AB79" s="9"/>
       <c r="AC79" s="9"/>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="48" t="s">
         <v>57</v>
       </c>
@@ -7221,7 +7228,7 @@
         <v>1.103246753246756E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="97" t="s">
         <v>115</v>
       </c>
@@ -7290,7 +7297,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" s="97" t="s">
         <v>115</v>
       </c>
@@ -7372,7 +7379,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" s="97" t="s">
         <v>115</v>
       </c>
@@ -7429,7 +7436,7 @@
       </c>
       <c r="AD83" s="29"/>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" s="97" t="s">
         <v>115</v>
       </c>
@@ -7485,7 +7492,7 @@
       </c>
       <c r="AD84" s="29"/>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" s="97" t="s">
         <v>115</v>
       </c>
@@ -7543,7 +7550,7 @@
       </c>
       <c r="AD85" s="91"/>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" s="97" t="s">
         <v>115</v>
       </c>
@@ -7597,7 +7604,7 @@
       <c r="AC86" s="61"/>
       <c r="AD86" s="29"/>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" s="97" t="s">
         <v>115</v>
       </c>
@@ -7642,7 +7649,7 @@
       <c r="AC87" s="9"/>
       <c r="AD87" s="29"/>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" s="97" t="s">
         <v>115</v>
       </c>
@@ -7686,7 +7693,7 @@
       <c r="AB88" s="9"/>
       <c r="AC88" s="9"/>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" s="97" t="s">
         <v>115</v>
       </c>
@@ -7730,7 +7737,7 @@
       <c r="AB89" s="9"/>
       <c r="AC89" s="9"/>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" s="97" t="s">
         <v>115</v>
       </c>
@@ -7773,7 +7780,7 @@
       <c r="AB90" s="9"/>
       <c r="AC90" s="9"/>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="97" t="s">
         <v>115</v>
       </c>
@@ -7816,7 +7823,7 @@
       <c r="AB91" s="9"/>
       <c r="AC91" s="9"/>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" s="97" t="s">
         <v>115</v>
       </c>
@@ -7859,7 +7866,7 @@
       <c r="AB92" s="9"/>
       <c r="AC92" s="9"/>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" s="97" t="s">
         <v>115</v>
       </c>
@@ -7902,7 +7909,7 @@
       <c r="AB93" s="9"/>
       <c r="AC93" s="9"/>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" s="97" t="s">
         <v>115</v>
       </c>
@@ -7960,7 +7967,7 @@
       <c r="AC94" s="20"/>
       <c r="AD94" s="21"/>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="97" t="s">
         <v>115</v>
       </c>
@@ -8018,7 +8025,7 @@
       <c r="AC95" s="20"/>
       <c r="AD95" s="21"/>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" s="97" t="s">
         <v>115</v>
       </c>
@@ -8075,7 +8082,7 @@
       <c r="AB96" s="9"/>
       <c r="AC96" s="9"/>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" s="97" t="s">
         <v>115</v>
       </c>
@@ -8118,7 +8125,7 @@
       <c r="AB97" s="9"/>
       <c r="AC97" s="9"/>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" s="97" t="s">
         <v>115</v>
       </c>
@@ -8194,7 +8201,7 @@
         <v>1.6977272727272674E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" s="97" t="s">
         <v>115</v>
       </c>
@@ -8269,7 +8276,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" s="97" t="s">
         <v>115</v>
       </c>
@@ -8349,7 +8356,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="97" t="s">
         <v>115</v>
       </c>
@@ -8412,7 +8419,7 @@
       <c r="AC101" s="61"/>
       <c r="AD101" s="29"/>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" s="97" t="s">
         <v>115</v>
       </c>
@@ -8454,7 +8461,7 @@
       <c r="AB102" s="9"/>
       <c r="AC102" s="9"/>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" s="97" t="s">
         <v>115</v>
       </c>
@@ -8516,7 +8523,7 @@
       <c r="AB103" s="9"/>
       <c r="AC103" s="9"/>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" s="97" t="s">
         <v>115</v>
       </c>
@@ -8579,7 +8586,7 @@
       <c r="AB104" s="9"/>
       <c r="AC104" s="9"/>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" s="97" t="s">
         <v>115</v>
       </c>
@@ -8655,7 +8662,7 @@
         <v>1.2202020202019992E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="97" t="s">
         <v>115</v>
       </c>
@@ -8730,7 +8737,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" s="97" t="s">
         <v>115</v>
       </c>
@@ -8810,7 +8817,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" s="97" t="s">
         <v>115</v>
       </c>
@@ -8873,7 +8880,7 @@
       <c r="AC108" s="61"/>
       <c r="AD108" s="29"/>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" s="97" t="s">
         <v>115</v>
       </c>
@@ -8915,7 +8922,7 @@
       <c r="AC109" s="61"/>
       <c r="AD109" s="29"/>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" s="97" t="s">
         <v>115</v>
       </c>
@@ -8957,7 +8964,7 @@
       <c r="AC110" s="61"/>
       <c r="AD110" s="29"/>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" s="97" t="s">
         <v>115</v>
       </c>
@@ -8999,7 +9006,7 @@
       <c r="AC111" s="61"/>
       <c r="AD111" s="29"/>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="97" t="s">
         <v>115</v>
       </c>
@@ -9042,7 +9049,7 @@
       <c r="AC112" s="9"/>
       <c r="AD112" s="29"/>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="97" t="s">
         <v>115</v>
       </c>
@@ -9084,7 +9091,7 @@
       <c r="AB113" s="9"/>
       <c r="AC113" s="9"/>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" s="97" t="s">
         <v>115</v>
       </c>
@@ -9146,7 +9153,7 @@
       <c r="AB114" s="9"/>
       <c r="AC114" s="9"/>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" s="97" t="s">
         <v>115</v>
       </c>
@@ -9208,7 +9215,7 @@
       <c r="AB115" s="9"/>
       <c r="AC115" s="9"/>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" s="97" t="s">
         <v>115</v>
       </c>
@@ -9253,7 +9260,7 @@
       <c r="AB116" s="9"/>
       <c r="AC116" s="9"/>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" s="97" t="s">
         <v>115</v>
       </c>
@@ -9329,7 +9336,7 @@
         <v>1.1939393939394138E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" s="97" t="s">
         <v>115</v>
       </c>
@@ -9404,7 +9411,7 @@
         <v>2.3699999999999999E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119" s="97" t="s">
         <v>115</v>
       </c>
@@ -9480,7 +9487,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" s="97" t="s">
         <v>115</v>
       </c>
@@ -9543,7 +9550,7 @@
       <c r="AC120" s="61"/>
       <c r="AD120" s="29"/>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" s="97" t="s">
         <v>115</v>
       </c>
@@ -9587,7 +9594,7 @@
       <c r="AC121" s="61"/>
       <c r="AD121" s="29"/>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" s="97" t="s">
         <v>115</v>
       </c>
@@ -9637,7 +9644,7 @@
       <c r="AC122" s="61"/>
       <c r="AD122" s="29"/>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" s="97" t="s">
         <v>115</v>
       </c>
@@ -9685,7 +9692,7 @@
       <c r="AC123" s="9"/>
       <c r="AD123" s="29"/>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" s="97" t="s">
         <v>115</v>
       </c>
@@ -9733,7 +9740,7 @@
       <c r="AC124" s="9"/>
       <c r="AD124" s="29"/>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125" s="97" t="s">
         <v>115</v>
       </c>
@@ -9775,7 +9782,7 @@
       <c r="AB125" s="9"/>
       <c r="AC125" s="9"/>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" s="97" t="s">
         <v>115</v>
       </c>
@@ -9817,7 +9824,7 @@
       <c r="AB126" s="9"/>
       <c r="AC126" s="9"/>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" s="97" t="s">
         <v>115</v>
       </c>
@@ -9859,7 +9866,7 @@
       <c r="AB127" s="9"/>
       <c r="AC127" s="9"/>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" s="97" t="s">
         <v>115</v>
       </c>
@@ -9901,7 +9908,7 @@
       <c r="AB128" s="9"/>
       <c r="AC128" s="9"/>
     </row>
-    <row r="129" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" s="97" t="s">
         <v>115</v>
       </c>
@@ -9963,7 +9970,7 @@
       <c r="AB129" s="9"/>
       <c r="AC129" s="9"/>
     </row>
-    <row r="130" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" s="97" t="s">
         <v>115</v>
       </c>
@@ -10026,7 +10033,7 @@
       <c r="AB130" s="9"/>
       <c r="AC130" s="9"/>
     </row>
-    <row r="131" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" s="97" t="s">
         <v>115</v>
       </c>
@@ -10102,7 +10109,7 @@
         <v>1.6918831168831194E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" s="97" t="s">
         <v>115</v>
       </c>
@@ -10187,7 +10194,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" s="97" t="s">
         <v>115</v>
       </c>
@@ -10263,7 +10270,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" s="97" t="s">
         <v>115</v>
       </c>
@@ -10326,7 +10333,7 @@
       <c r="AC134" s="106"/>
       <c r="AD134" s="107"/>
     </row>
-    <row r="135" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135" s="97" t="s">
         <v>115</v>
       </c>
@@ -10386,7 +10393,7 @@
       </c>
       <c r="AF135" s="32"/>
     </row>
-    <row r="136" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136" s="97" t="s">
         <v>115</v>
       </c>
@@ -10451,7 +10458,7 @@
       <c r="AB136" s="9"/>
       <c r="AC136" s="9"/>
     </row>
-    <row r="137" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" s="97" t="s">
         <v>115</v>
       </c>
@@ -10526,7 +10533,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" s="97" t="s">
         <v>115</v>
       </c>
@@ -10612,7 +10619,7 @@
         <v>2.4196468990493547E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139" s="97" t="s">
         <v>115</v>
       </c>
@@ -10681,7 +10688,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140" s="97" t="s">
         <v>115</v>
       </c>
@@ -10751,7 +10758,7 @@
         <v>1.2800000000000001E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" s="97" t="s">
         <v>115</v>
       </c>
@@ -10825,7 +10832,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" s="97" t="s">
         <v>115</v>
       </c>
@@ -10882,7 +10889,7 @@
       </c>
       <c r="AD142" s="29"/>
     </row>
-    <row r="143" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" s="97" t="s">
         <v>115</v>
       </c>
@@ -10938,7 +10945,7 @@
       </c>
       <c r="AD143" s="29"/>
     </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144" s="97" t="s">
         <v>115</v>
       </c>
@@ -10994,7 +11001,7 @@
       </c>
       <c r="AD144" s="91"/>
     </row>
-    <row r="145" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" s="97" t="s">
         <v>115</v>
       </c>
@@ -11050,7 +11057,7 @@
       </c>
       <c r="AD145" s="29"/>
     </row>
-    <row r="146" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146" s="97" t="s">
         <v>115</v>
       </c>
@@ -11106,7 +11113,7 @@
         <v>173.309</v>
       </c>
     </row>
-    <row r="147" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147" s="97" t="s">
         <v>115</v>
       </c>
@@ -11164,7 +11171,7 @@
       </c>
       <c r="AD147" s="21"/>
     </row>
-    <row r="148" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" s="97" t="s">
         <v>115</v>
       </c>
@@ -11222,7 +11229,7 @@
       <c r="AB148" s="9"/>
       <c r="AC148" s="9"/>
     </row>
-    <row r="149" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" s="97" t="s">
         <v>115</v>
       </c>
@@ -11266,7 +11273,7 @@
       <c r="AB149" s="9"/>
       <c r="AC149" s="9"/>
     </row>
-    <row r="150" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" s="97" t="s">
         <v>115</v>
       </c>
@@ -11299,7 +11306,7 @@
       <c r="AB150" s="9"/>
       <c r="AC150" s="9"/>
     </row>
-    <row r="151" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" s="97" t="s">
         <v>115</v>
       </c>
@@ -11332,7 +11339,7 @@
       <c r="AB151" s="9"/>
       <c r="AC151" s="9"/>
     </row>
-    <row r="152" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" s="97" t="s">
         <v>115</v>
       </c>
@@ -11388,7 +11395,7 @@
       </c>
       <c r="AF152" s="32"/>
     </row>
-    <row r="153" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" s="97" t="s">
         <v>115</v>
       </c>
@@ -11443,7 +11450,7 @@
       <c r="AB153" s="9"/>
       <c r="AC153" s="9"/>
     </row>
-    <row r="154" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" s="97" t="s">
         <v>115</v>
       </c>
@@ -11498,7 +11505,7 @@
       <c r="AB154" s="9"/>
       <c r="AC154" s="9"/>
     </row>
-    <row r="155" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" s="97" t="s">
         <v>115</v>
       </c>
@@ -11543,7 +11550,7 @@
       <c r="AB155" s="9"/>
       <c r="AC155" s="9"/>
     </row>
-    <row r="156" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156" s="97" t="s">
         <v>115</v>
       </c>
@@ -11613,7 +11620,7 @@
         <v>1.5518181818181764E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157" s="97" t="s">
         <v>115</v>
       </c>
@@ -11682,7 +11689,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="158" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" s="97" t="s">
         <v>115</v>
       </c>
@@ -11755,7 +11762,7 @@
         <v>1.54E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" s="97" t="s">
         <v>115</v>
       </c>
@@ -11831,7 +11838,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="160" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" s="97" t="s">
         <v>115</v>
       </c>
@@ -11896,7 +11903,7 @@
       <c r="AB160" s="9"/>
       <c r="AC160" s="9"/>
     </row>
-    <row r="161" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" s="97" t="s">
         <v>115</v>
       </c>
@@ -11961,7 +11968,7 @@
       <c r="AB161" s="9"/>
       <c r="AC161" s="9"/>
     </row>
-    <row r="162" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" s="97" t="s">
         <v>115</v>
       </c>
@@ -12017,7 +12024,7 @@
       </c>
       <c r="AF162" s="32"/>
     </row>
-    <row r="163" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" s="97" t="s">
         <v>115</v>
       </c>
@@ -12070,7 +12077,7 @@
       <c r="AB163" s="9"/>
       <c r="AC163" s="9"/>
     </row>
-    <row r="164" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164" s="97" t="s">
         <v>115</v>
       </c>
@@ -12123,7 +12130,7 @@
       <c r="AB164" s="9"/>
       <c r="AC164" s="9"/>
     </row>
-    <row r="165" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A165" s="97" t="s">
         <v>115</v>
       </c>
@@ -12193,7 +12200,7 @@
         <v>1.7022727272727356E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166" s="97" t="s">
         <v>115</v>
       </c>
@@ -12262,7 +12269,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="167" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A167" s="97" t="s">
         <v>115</v>
       </c>
@@ -12334,7 +12341,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="168" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168" s="97" t="s">
         <v>115</v>
       </c>
@@ -12404,7 +12411,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="169" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" s="97" t="s">
         <v>115</v>
       </c>
@@ -12476,7 +12483,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="170" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" s="97" t="s">
         <v>115</v>
       </c>
@@ -12537,7 +12544,7 @@
       <c r="AC170" s="61"/>
       <c r="AD170" s="29"/>
     </row>
-    <row r="171" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" s="97" t="s">
         <v>115</v>
       </c>
@@ -12591,7 +12598,7 @@
       <c r="AC171" s="9"/>
       <c r="AD171" s="29"/>
     </row>
-    <row r="172" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" s="97" t="s">
         <v>115</v>
       </c>
@@ -12643,7 +12650,7 @@
       <c r="AC172" s="20"/>
       <c r="AD172" s="91"/>
     </row>
-    <row r="173" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" s="97" t="s">
         <v>115</v>
       </c>
@@ -12685,7 +12692,7 @@
       <c r="AC173" s="9"/>
       <c r="AD173" s="29"/>
     </row>
-    <row r="174" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" s="97" t="s">
         <v>115</v>
       </c>
@@ -12741,7 +12748,7 @@
       </c>
       <c r="AF174" s="32"/>
     </row>
-    <row r="175" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175" s="97" t="s">
         <v>115</v>
       </c>
@@ -12806,7 +12813,7 @@
       <c r="AB175" s="9"/>
       <c r="AC175" s="9"/>
     </row>
-    <row r="176" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176" s="97" t="s">
         <v>115</v>
       </c>
@@ -12871,7 +12878,7 @@
       <c r="AB176" s="9"/>
       <c r="AC176" s="9"/>
     </row>
-    <row r="177" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A177" s="97" t="s">
         <v>115</v>
       </c>
@@ -12936,7 +12943,7 @@
       <c r="AB177" s="9"/>
       <c r="AC177" s="9"/>
     </row>
-    <row r="178" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" s="97" t="s">
         <v>115</v>
       </c>
@@ -13001,7 +13008,7 @@
       <c r="AB178" s="9"/>
       <c r="AC178" s="9"/>
     </row>
-    <row r="179" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" s="97" t="s">
         <v>115</v>
       </c>
@@ -13061,7 +13068,7 @@
       <c r="AC179" s="20"/>
       <c r="AD179" s="21"/>
     </row>
-    <row r="180" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180" s="97" t="s">
         <v>115</v>
       </c>
@@ -13121,7 +13128,7 @@
       <c r="AC180" s="20"/>
       <c r="AD180" s="21"/>
     </row>
-    <row r="181" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" s="97" t="s">
         <v>115</v>
       </c>
@@ -13191,7 +13198,7 @@
         <v>2.2829545454545408E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" s="97" t="s">
         <v>115</v>
       </c>
@@ -13260,7 +13267,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183" s="97" t="s">
         <v>115</v>
       </c>
@@ -13324,7 +13331,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="184" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" s="97" t="s">
         <v>115</v>
       </c>
@@ -13400,7 +13407,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="185" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A185" s="97" t="s">
         <v>115</v>
       </c>
@@ -13472,7 +13479,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="186" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" s="97" t="s">
         <v>115</v>
       </c>
@@ -13535,7 +13542,7 @@
       <c r="AC186" s="61"/>
       <c r="AD186" s="29"/>
     </row>
-    <row r="187" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" s="97" t="s">
         <v>115</v>
       </c>
@@ -13579,7 +13586,7 @@
       <c r="AC187" s="20"/>
       <c r="AD187" s="91"/>
     </row>
-    <row r="188" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188" s="97" t="s">
         <v>115</v>
       </c>
@@ -13642,7 +13649,7 @@
       <c r="AC188" s="9"/>
       <c r="AD188" s="29"/>
     </row>
-    <row r="189" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A189" s="97" t="s">
         <v>115</v>
       </c>
@@ -13708,7 +13715,7 @@
       <c r="AB189" s="9"/>
       <c r="AC189" s="9"/>
     </row>
-    <row r="190" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" s="97" t="s">
         <v>115</v>
       </c>
@@ -13752,7 +13759,7 @@
       <c r="AC190" s="20"/>
       <c r="AD190" s="91"/>
     </row>
-    <row r="191" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191" s="97" t="s">
         <v>115</v>
       </c>
@@ -13815,7 +13822,7 @@
       <c r="AC191" s="9"/>
       <c r="AD191" s="29"/>
     </row>
-    <row r="192" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192" s="97" t="s">
         <v>115</v>
       </c>
@@ -13871,7 +13878,7 @@
       </c>
       <c r="AF192" s="32"/>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193" s="97" t="s">
         <v>115</v>
       </c>
@@ -13936,7 +13943,7 @@
       <c r="AB193" s="9"/>
       <c r="AC193" s="9"/>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A194" s="97" t="s">
         <v>115</v>
       </c>
@@ -14001,7 +14008,7 @@
       <c r="AB194" s="9"/>
       <c r="AC194" s="9"/>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195" s="97" t="s">
         <v>115</v>
       </c>
@@ -14054,7 +14061,7 @@
       <c r="AB195" s="9"/>
       <c r="AC195" s="9"/>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196" s="97" t="s">
         <v>115</v>
       </c>
@@ -14111,7 +14118,7 @@
       <c r="AB196" s="9"/>
       <c r="AC196" s="9"/>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" s="97" t="s">
         <v>115</v>
       </c>
@@ -14155,7 +14162,7 @@
       <c r="AC197" s="20"/>
       <c r="AD197" s="21"/>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198" s="97" t="s">
         <v>115</v>
       </c>
@@ -14199,7 +14206,7 @@
       <c r="AB198" s="9"/>
       <c r="AC198" s="9"/>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199" s="97" t="s">
         <v>115</v>
       </c>
@@ -14269,7 +14276,7 @@
         <v>1.6599999999999948E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" s="97" t="s">
         <v>115</v>
       </c>
@@ -14338,7 +14345,7 @@
         <v>2.8199999999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A201" s="97" t="s">
         <v>115</v>
       </c>
@@ -14410,7 +14417,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" s="97" t="s">
         <v>115</v>
       </c>
@@ -14476,7 +14483,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" s="97" t="s">
         <v>115</v>
       </c>
@@ -14550,7 +14557,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" s="97" t="s">
         <v>115</v>
       </c>
@@ -14607,7 +14614,7 @@
       <c r="AC204" s="61"/>
       <c r="AD204" s="29"/>
     </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" s="97" t="s">
         <v>115</v>
       </c>
@@ -14674,7 +14681,7 @@
       <c r="AC205" s="61"/>
       <c r="AD205" s="29"/>
     </row>
-    <row r="206" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" s="97" t="s">
         <v>115</v>
       </c>
@@ -14717,7 +14724,7 @@
       <c r="AC206" s="61"/>
       <c r="AD206" s="29"/>
     </row>
-    <row r="207" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" s="97" t="s">
         <v>115</v>
       </c>
@@ -14761,7 +14768,7 @@
       <c r="AC207" s="86"/>
       <c r="AD207" s="91"/>
     </row>
-    <row r="208" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" s="97" t="s">
         <v>115</v>
       </c>
@@ -14825,7 +14832,7 @@
       <c r="AC208" s="86"/>
       <c r="AD208" s="91"/>
     </row>
-    <row r="209" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" s="97" t="s">
         <v>115</v>
       </c>
@@ -14889,7 +14896,7 @@
       <c r="AB209" s="9"/>
       <c r="AC209" s="9"/>
     </row>
-    <row r="210" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210" s="97" t="s">
         <v>115</v>
       </c>
@@ -14945,7 +14952,7 @@
       <c r="AB210" s="9"/>
       <c r="AC210" s="9"/>
     </row>
-    <row r="211" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211" s="97" t="s">
         <v>115</v>
       </c>
@@ -15001,7 +15008,7 @@
       <c r="AB211" s="9"/>
       <c r="AC211" s="9"/>
     </row>
-    <row r="212" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212" s="97" t="s">
         <v>115</v>
       </c>
@@ -15067,7 +15074,7 @@
       <c r="AC212" s="86"/>
       <c r="AD212" s="91"/>
     </row>
-    <row r="213" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213" s="97" t="s">
         <v>115</v>
       </c>
@@ -15111,7 +15118,7 @@
       <c r="AC213" s="20"/>
       <c r="AD213" s="21"/>
     </row>
-    <row r="214" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214" s="97" t="s">
         <v>115</v>
       </c>
@@ -15155,7 +15162,7 @@
       <c r="AB214" s="9"/>
       <c r="AC214" s="9"/>
     </row>
-    <row r="215" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" s="97" t="s">
         <v>115</v>
       </c>
@@ -15211,7 +15218,7 @@
       </c>
       <c r="AF215" s="32"/>
     </row>
-    <row r="216" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216" s="97" t="s">
         <v>115</v>
       </c>
@@ -15278,7 +15285,7 @@
       <c r="AB216" s="9"/>
       <c r="AC216" s="9"/>
     </row>
-    <row r="217" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217" s="97" t="s">
         <v>115</v>
       </c>
@@ -15345,7 +15352,7 @@
       <c r="AB217" s="9"/>
       <c r="AC217" s="9"/>
     </row>
-    <row r="218" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" s="97" t="s">
         <v>115</v>
       </c>
@@ -15412,7 +15419,7 @@
       <c r="AB218" s="9"/>
       <c r="AC218" s="9"/>
     </row>
-    <row r="219" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" s="97" t="s">
         <v>115</v>
       </c>
@@ -15479,7 +15486,7 @@
       <c r="AB219" s="9"/>
       <c r="AC219" s="9"/>
     </row>
-    <row r="220" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" s="97" t="s">
         <v>115</v>
       </c>
@@ -15523,7 +15530,7 @@
       <c r="AC220" s="20"/>
       <c r="AD220" s="21"/>
     </row>
-    <row r="221" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" s="97" t="s">
         <v>115</v>
       </c>
@@ -15567,7 +15574,7 @@
       <c r="AC221" s="20"/>
       <c r="AD221" s="21"/>
     </row>
-    <row r="222" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222" s="97" t="s">
         <v>115</v>
       </c>
@@ -15639,7 +15646,7 @@
         <v>3.1027739881764438E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" s="97" t="s">
         <v>115</v>
       </c>
@@ -15710,7 +15717,7 @@
         <v>2.7699999999999999E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" s="97" t="s">
         <v>115</v>
       </c>
@@ -15786,7 +15793,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="225" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" s="97" t="s">
         <v>115</v>
       </c>
@@ -15853,7 +15860,7 @@
       <c r="AC225" s="61"/>
       <c r="AD225" s="29"/>
     </row>
-    <row r="226" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" s="97" t="s">
         <v>115</v>
       </c>
@@ -15897,7 +15904,7 @@
       <c r="AB226" s="9"/>
       <c r="AC226" s="9"/>
     </row>
-    <row r="227" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" s="97" t="s">
         <v>115</v>
       </c>
@@ -15953,7 +15960,7 @@
       </c>
       <c r="AF227" s="32"/>
     </row>
-    <row r="228" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" s="97" t="s">
         <v>115</v>
       </c>
@@ -15996,7 +16003,7 @@
       <c r="AB228" s="9"/>
       <c r="AC228" s="9"/>
     </row>
-    <row r="229" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" s="97" t="s">
         <v>115</v>
       </c>
@@ -16039,7 +16046,7 @@
       <c r="AB229" s="9"/>
       <c r="AC229" s="9"/>
     </row>
-    <row r="230" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" s="97" t="s">
         <v>115</v>
       </c>
@@ -16104,7 +16111,7 @@
       <c r="AB230" s="9"/>
       <c r="AC230" s="9"/>
     </row>
-    <row r="231" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231" s="97" t="s">
         <v>115</v>
       </c>
@@ -16169,7 +16176,7 @@
       <c r="AB231" s="9"/>
       <c r="AC231" s="9"/>
     </row>
-    <row r="232" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232" s="97" t="s">
         <v>115</v>
       </c>
@@ -16212,7 +16219,7 @@
       <c r="AB232" s="9"/>
       <c r="AC232" s="9"/>
     </row>
-    <row r="233" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233" s="97" t="s">
         <v>115</v>
       </c>
@@ -16256,7 +16263,7 @@
       <c r="AB233" s="9"/>
       <c r="AC233" s="9"/>
     </row>
-    <row r="234" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234" s="97" t="s">
         <v>115</v>
       </c>
@@ -16328,7 +16335,7 @@
         <v>3.3560606060606069E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235" s="97" t="s">
         <v>115</v>
       </c>
@@ -16401,7 +16408,7 @@
         <v>3.6499999999999998E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236" s="97" t="s">
         <v>115</v>
       </c>
@@ -16467,7 +16474,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="237" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237" s="97" t="s">
         <v>115</v>
       </c>
@@ -16545,7 +16552,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="238" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238" s="97" t="s">
         <v>115</v>
       </c>
@@ -16609,7 +16616,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="239" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" s="97" t="s">
         <v>115</v>
       </c>
@@ -16667,7 +16674,7 @@
       <c r="AC239" s="61"/>
       <c r="AD239" s="29"/>
     </row>
-    <row r="240" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240" s="97" t="s">
         <v>115</v>
       </c>
@@ -16736,7 +16743,7 @@
       <c r="AC240" s="61"/>
       <c r="AD240" s="29"/>
     </row>
-    <row r="241" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241" s="97" t="s">
         <v>115</v>
       </c>
@@ -16791,7 +16798,7 @@
       <c r="AC241" s="61"/>
       <c r="AD241" s="29"/>
     </row>
-    <row r="242" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" s="97" t="s">
         <v>115</v>
       </c>
@@ -16853,7 +16860,7 @@
       <c r="AC242" s="86"/>
       <c r="AD242" s="91"/>
     </row>
-    <row r="243" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" s="97" t="s">
         <v>115</v>
       </c>
@@ -16897,7 +16904,7 @@
       <c r="AB243" s="9"/>
       <c r="AC243" s="9"/>
     </row>
-    <row r="244" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244" s="97" t="s">
         <v>115</v>
       </c>
@@ -16953,7 +16960,7 @@
       </c>
       <c r="AF244" s="32"/>
     </row>
-    <row r="245" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" s="97" t="s">
         <v>115</v>
       </c>
@@ -16996,7 +17003,7 @@
       <c r="AB245" s="9"/>
       <c r="AC245" s="9"/>
     </row>
-    <row r="246" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A246" s="97" t="s">
         <v>115</v>
       </c>
@@ -17050,7 +17057,7 @@
       <c r="AB246" s="9"/>
       <c r="AC246" s="9"/>
     </row>
-    <row r="247" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247" s="97" t="s">
         <v>115</v>
       </c>
@@ -17115,7 +17122,7 @@
       <c r="AB247" s="9"/>
       <c r="AC247" s="9"/>
     </row>
-    <row r="248" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248" s="97" t="s">
         <v>115</v>
       </c>
@@ -17180,7 +17187,7 @@
       <c r="AB248" s="9"/>
       <c r="AC248" s="9"/>
     </row>
-    <row r="249" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249" s="97" t="s">
         <v>115</v>
       </c>
@@ -17234,7 +17241,7 @@
       <c r="AC249" s="20"/>
       <c r="AD249" s="21"/>
     </row>
-    <row r="250" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" s="97" t="s">
         <v>115</v>
       </c>
@@ -17288,7 +17295,7 @@
       <c r="AC250" s="20"/>
       <c r="AD250" s="21"/>
     </row>
-    <row r="251" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" s="97" t="s">
         <v>115</v>
       </c>
@@ -17362,7 +17369,7 @@
         <v>3.8397727272727278E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A252" s="97" t="s">
         <v>115</v>
       </c>
@@ -17435,7 +17442,7 @@
         <v>6.3500000000000001E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A253" s="97" t="s">
         <v>115</v>
       </c>
@@ -17500,7 +17507,7 @@
       <c r="AC253" s="62"/>
       <c r="AD253" s="126"/>
     </row>
-    <row r="254" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" s="97" t="s">
         <v>115</v>
       </c>
@@ -17574,7 +17581,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="255" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" s="97" t="s">
         <v>115</v>
       </c>
@@ -17626,7 +17633,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="256" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256" s="97" t="s">
         <v>115</v>
       </c>
@@ -17704,7 +17711,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="257" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257" s="97" t="s">
         <v>115</v>
       </c>
@@ -17748,7 +17755,7 @@
       <c r="AC257" s="86"/>
       <c r="AD257" s="91"/>
     </row>
-    <row r="258" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258" s="97" t="s">
         <v>115</v>
       </c>
@@ -17805,7 +17812,7 @@
       <c r="AC258" s="9"/>
       <c r="AD258" s="29"/>
     </row>
-    <row r="259" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A259" s="97" t="s">
         <v>115</v>
       </c>
@@ -17873,7 +17880,7 @@
       <c r="AB259" s="9"/>
       <c r="AC259" s="9"/>
     </row>
-    <row r="260" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" s="97" t="s">
         <v>115</v>
       </c>
@@ -17914,7 +17921,7 @@
       <c r="AC260" s="86"/>
       <c r="AD260" s="91"/>
     </row>
-    <row r="261" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261" s="97" t="s">
         <v>115</v>
       </c>
@@ -17969,7 +17976,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="262" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262" s="97" t="s">
         <v>115</v>
       </c>
@@ -18013,7 +18020,7 @@
       <c r="AB262" s="9"/>
       <c r="AC262" s="9"/>
     </row>
-    <row r="263" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263" s="97" t="s">
         <v>115</v>
       </c>
@@ -18075,7 +18082,7 @@
       <c r="AB263" s="9"/>
       <c r="AC263" s="9"/>
     </row>
-    <row r="264" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A264" s="97" t="s">
         <v>115</v>
       </c>
@@ -18140,7 +18147,7 @@
       <c r="AB264" s="9"/>
       <c r="AC264" s="9"/>
     </row>
-    <row r="265" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265" s="97" t="s">
         <v>115</v>
       </c>
@@ -18205,7 +18212,7 @@
       <c r="AB265" s="9"/>
       <c r="AC265" s="9"/>
     </row>
-    <row r="266" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266" s="97" t="s">
         <v>115</v>
       </c>
@@ -18246,7 +18253,7 @@
       <c r="AC266" s="20"/>
       <c r="AD266" s="21"/>
     </row>
-    <row r="267" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267" s="97" t="s">
         <v>115</v>
       </c>
@@ -18320,7 +18327,7 @@
         <v>5.2856060606060629E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268" s="97" t="s">
         <v>115</v>
       </c>
@@ -18393,7 +18400,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A269" s="97" t="s">
         <v>115</v>
       </c>
@@ -18471,7 +18478,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="270" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270" s="97" t="s">
         <v>115</v>
       </c>
@@ -18551,7 +18558,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="271" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271" s="97" t="s">
         <v>115</v>
       </c>
@@ -18605,7 +18612,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="272" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272" s="97" t="s">
         <v>115</v>
       </c>
@@ -18650,7 +18657,7 @@
       <c r="AC272" s="61"/>
       <c r="AD272" s="126"/>
     </row>
-    <row r="273" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273" s="97" t="s">
         <v>115</v>
       </c>
@@ -18705,7 +18712,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="274" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A274" s="97" t="s">
         <v>115</v>
       </c>
@@ -18762,7 +18769,7 @@
       <c r="AC274" s="9"/>
       <c r="AD274" s="29"/>
     </row>
-    <row r="275" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A275" s="97" t="s">
         <v>115</v>
       </c>
@@ -18824,7 +18831,7 @@
       <c r="AB275" s="9"/>
       <c r="AC275" s="9"/>
     </row>
-    <row r="276" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276" s="97" t="s">
         <v>115</v>
       </c>
@@ -18887,7 +18894,7 @@
       <c r="AC276" s="61"/>
       <c r="AD276" s="29"/>
     </row>
-    <row r="277" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A277" s="97" t="s">
         <v>115</v>
       </c>
@@ -18947,7 +18954,7 @@
       <c r="AC277" s="21"/>
       <c r="AD277" s="21"/>
     </row>
-    <row r="278" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278" s="97" t="s">
         <v>115</v>
       </c>
@@ -18992,7 +18999,7 @@
       <c r="AB278" s="9"/>
       <c r="AC278" s="9"/>
     </row>
-    <row r="279" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279" s="97" t="s">
         <v>115</v>
       </c>
@@ -19066,7 +19073,7 @@
         <v>3.8438095238095271E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A280" s="97" t="s">
         <v>115</v>
       </c>
@@ -19139,7 +19146,7 @@
         <v>3.85E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281" s="97" t="s">
         <v>115</v>
       </c>
@@ -19217,7 +19224,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="282" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282" s="97" t="s">
         <v>115</v>
       </c>
@@ -19295,7 +19302,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A283" s="97" t="s">
         <v>115</v>
       </c>
@@ -19370,7 +19377,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="284" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284" s="97" t="s">
         <v>115</v>
       </c>
@@ -19438,7 +19445,7 @@
       <c r="AB284" s="9"/>
       <c r="AC284" s="9"/>
     </row>
-    <row r="285" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285" s="97" t="s">
         <v>115</v>
       </c>
@@ -19503,7 +19510,7 @@
       <c r="AC285" s="61"/>
       <c r="AD285" s="29"/>
     </row>
-    <row r="286" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A286" s="97" t="s">
         <v>115</v>
       </c>
@@ -19565,7 +19572,7 @@
       <c r="AC286" s="86"/>
       <c r="AD286" s="91"/>
     </row>
-    <row r="287" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287" s="97" t="s">
         <v>115</v>
       </c>
@@ -19633,7 +19640,7 @@
       <c r="AB287" s="9"/>
       <c r="AC287" s="9"/>
     </row>
-    <row r="288" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288" s="97" t="s">
         <v>115</v>
       </c>
@@ -19678,7 +19685,7 @@
       <c r="S288" s="60"/>
       <c r="V288" s="146"/>
     </row>
-    <row r="289" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A289" s="97" t="s">
         <v>115</v>
       </c>
@@ -19730,7 +19737,7 @@
       <c r="AC289" s="86"/>
       <c r="AD289" s="91"/>
     </row>
-    <row r="290" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290" s="97" t="s">
         <v>115</v>
       </c>
@@ -19786,7 +19793,7 @@
       </c>
       <c r="AF290" s="32"/>
     </row>
-    <row r="291" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291" s="97" t="s">
         <v>115</v>
       </c>
@@ -19851,7 +19858,7 @@
       <c r="AB291" s="9"/>
       <c r="AC291" s="9"/>
     </row>
-    <row r="292" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292" s="97" t="s">
         <v>115</v>
       </c>
@@ -19916,7 +19923,7 @@
       <c r="AB292" s="9"/>
       <c r="AC292" s="9"/>
     </row>
-    <row r="293" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293" s="97" t="s">
         <v>115</v>
       </c>
@@ -19978,7 +19985,7 @@
       <c r="AB293" s="9"/>
       <c r="AC293" s="9"/>
     </row>
-    <row r="294" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A294" s="97" t="s">
         <v>115</v>
       </c>
@@ -20038,7 +20045,7 @@
       <c r="AC294" s="20"/>
       <c r="AD294" s="21"/>
     </row>
-    <row r="295" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295" s="97" t="s">
         <v>115</v>
       </c>
@@ -20082,7 +20089,7 @@
       <c r="AB295" s="9"/>
       <c r="AC295" s="9"/>
     </row>
-    <row r="296" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296" s="97" t="s">
         <v>115</v>
       </c>
@@ -20156,7 +20163,7 @@
         <v>4.2545959595959637E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297" s="97" t="s">
         <v>115</v>
       </c>
@@ -20229,7 +20236,7 @@
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298" s="97" t="s">
         <v>115</v>
       </c>
@@ -20307,7 +20314,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="299" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A299" s="97" t="s">
         <v>115</v>
       </c>
@@ -20385,7 +20392,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="300" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A300" s="97" t="s">
         <v>115</v>
       </c>
@@ -20459,7 +20466,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="301" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301" s="97" t="s">
         <v>115</v>
       </c>
@@ -20519,7 +20526,7 @@
       <c r="AC301" s="20"/>
       <c r="AD301" s="21"/>
     </row>
-    <row r="302" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A302" s="97" t="s">
         <v>115</v>
       </c>
@@ -20590,7 +20597,7 @@
       <c r="AC302" s="9"/>
       <c r="AD302" s="29"/>
     </row>
-    <row r="303" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A303" s="97" t="s">
         <v>115</v>
       </c>
@@ -20653,7 +20660,7 @@
       <c r="AC303" s="9"/>
       <c r="AD303" s="29"/>
     </row>
-    <row r="304" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A304" s="97" t="s">
         <v>115</v>
       </c>
@@ -20713,7 +20720,7 @@
       <c r="AC304" s="20"/>
       <c r="AD304" s="21"/>
     </row>
-    <row r="305" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A305" s="97" t="s">
         <v>115</v>
       </c>
@@ -20757,7 +20764,7 @@
       <c r="AB305" s="9"/>
       <c r="AC305" s="9"/>
     </row>
-    <row r="306" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A306" s="97" t="s">
         <v>115</v>
       </c>
@@ -20813,7 +20820,7 @@
       </c>
       <c r="AF306" s="32"/>
     </row>
-    <row r="307" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A307" s="97" t="s">
         <v>115</v>
       </c>
@@ -20875,7 +20882,7 @@
       <c r="AB307" s="9"/>
       <c r="AC307" s="9"/>
     </row>
-    <row r="308" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A308" s="97" t="s">
         <v>115</v>
       </c>
@@ -20940,7 +20947,7 @@
       <c r="AB308" s="9"/>
       <c r="AC308" s="9"/>
     </row>
-    <row r="309" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309" s="97" t="s">
         <v>115</v>
       </c>
@@ -21005,7 +21012,7 @@
       <c r="AB309" s="9"/>
       <c r="AC309" s="9"/>
     </row>
-    <row r="310" spans="1:32" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:32" ht="15.75" hidden="1" x14ac:dyDescent="0.5">
       <c r="A310" s="97" t="s">
         <v>115</v>
       </c>
@@ -21065,7 +21072,7 @@
       <c r="AC310" s="20"/>
       <c r="AD310" s="21"/>
     </row>
-    <row r="311" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311" s="97" t="s">
         <v>115</v>
       </c>
@@ -21139,7 +21146,7 @@
         <v>3.8193181818181654E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A312" s="97" t="s">
         <v>115</v>
       </c>
@@ -21212,7 +21219,7 @@
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A313" s="97" t="s">
         <v>115</v>
       </c>
@@ -21290,7 +21297,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="314" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A314" s="97" t="s">
         <v>115</v>
       </c>
@@ -21368,7 +21375,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="315" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A315" s="97" t="s">
         <v>115</v>
       </c>
@@ -21442,7 +21449,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="316" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A316" s="97" t="s">
         <v>115</v>
       </c>
@@ -21502,7 +21509,7 @@
       <c r="AC316" s="86"/>
       <c r="AD316" s="154"/>
     </row>
-    <row r="317" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A317" s="97" t="s">
         <v>115</v>
       </c>
@@ -21573,7 +21580,7 @@
       <c r="AC317" s="9"/>
       <c r="AD317" s="29"/>
     </row>
-    <row r="318" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A318" s="97" t="s">
         <v>115</v>
       </c>
@@ -21636,7 +21643,7 @@
       <c r="AC318" s="9"/>
       <c r="AD318" s="29"/>
     </row>
-    <row r="319" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A319" s="97" t="s">
         <v>115</v>
       </c>
@@ -21696,7 +21703,7 @@
       <c r="AC319" s="20"/>
       <c r="AD319" s="21"/>
     </row>
-    <row r="320" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320" s="97" t="s">
         <v>115</v>
       </c>
@@ -21740,7 +21747,7 @@
       <c r="AB320" s="9"/>
       <c r="AC320" s="9"/>
     </row>
-    <row r="321" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A321" s="97" t="s">
         <v>115</v>
       </c>
@@ -21796,7 +21803,7 @@
       </c>
       <c r="AF321" s="32"/>
     </row>
-    <row r="322" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A322" s="97" t="s">
         <v>115</v>
       </c>
@@ -21858,7 +21865,7 @@
       <c r="AB322" s="9"/>
       <c r="AC322" s="9"/>
     </row>
-    <row r="323" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" s="97" t="s">
         <v>115</v>
       </c>
@@ -21923,7 +21930,7 @@
       <c r="AB323" s="9"/>
       <c r="AC323" s="9"/>
     </row>
-    <row r="324" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A324" s="97" t="s">
         <v>115</v>
       </c>
@@ -21988,7 +21995,7 @@
       <c r="AB324" s="9"/>
       <c r="AC324" s="9"/>
     </row>
-    <row r="325" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A325" s="97" t="s">
         <v>115</v>
       </c>
@@ -22048,7 +22055,7 @@
       <c r="AC325" s="20"/>
       <c r="AD325" s="21"/>
     </row>
-    <row r="326" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A326" s="97" t="s">
         <v>115</v>
       </c>
@@ -22122,7 +22129,7 @@
         <v>3.8136363636363524E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A327" s="97" t="s">
         <v>115</v>
       </c>
@@ -22195,7 +22202,7 @@
         <v>2.6200000000000001E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A328" s="97" t="s">
         <v>115</v>
       </c>
@@ -22259,7 +22266,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="329" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A329" s="97" t="s">
         <v>115</v>
       </c>
@@ -22333,7 +22340,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="330" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A330" s="97" t="s">
         <v>115</v>
       </c>
@@ -22411,7 +22418,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="331" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331" s="97" t="s">
         <v>115</v>
       </c>
@@ -22473,7 +22480,7 @@
       <c r="AC331" s="86"/>
       <c r="AD331" s="91"/>
     </row>
-    <row r="332" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A332" s="97" t="s">
         <v>115</v>
       </c>
@@ -22536,7 +22543,7 @@
       <c r="AC332" s="9"/>
       <c r="AD332" s="29"/>
     </row>
-    <row r="333" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A333" s="97" t="s">
         <v>115</v>
       </c>
@@ -22608,7 +22615,7 @@
       <c r="AC333" s="9"/>
       <c r="AD333" s="29"/>
     </row>
-    <row r="334" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A334" s="97" t="s">
         <v>115</v>
       </c>
@@ -22668,7 +22675,7 @@
       <c r="AC334" s="20"/>
       <c r="AD334" s="91"/>
     </row>
-    <row r="335" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A335" s="97" t="s">
         <v>115</v>
       </c>
@@ -22724,7 +22731,7 @@
       </c>
       <c r="AF335" s="32"/>
     </row>
-    <row r="336" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A336" s="97" t="s">
         <v>115</v>
       </c>
@@ -22768,7 +22775,7 @@
       <c r="AB336" s="9"/>
       <c r="AC336" s="9"/>
     </row>
-    <row r="337" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A337" s="97" t="s">
         <v>115</v>
       </c>
@@ -22830,7 +22837,7 @@
       <c r="AB337" s="9"/>
       <c r="AC337" s="9"/>
     </row>
-    <row r="338" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338" s="97" t="s">
         <v>115</v>
       </c>
@@ -22895,7 +22902,7 @@
       <c r="AB338" s="9"/>
       <c r="AC338" s="9"/>
     </row>
-    <row r="339" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339" s="97" t="s">
         <v>115</v>
       </c>
@@ -22960,7 +22967,7 @@
       <c r="AB339" s="9"/>
       <c r="AC339" s="9"/>
     </row>
-    <row r="340" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A340" s="97" t="s">
         <v>115</v>
       </c>
@@ -23004,7 +23011,7 @@
       <c r="AC340" s="20"/>
       <c r="AD340" s="21"/>
     </row>
-    <row r="341" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341" s="97" t="s">
         <v>115</v>
       </c>
@@ -23049,7 +23056,7 @@
       <c r="AB341" s="9"/>
       <c r="AC341" s="9"/>
     </row>
-    <row r="342" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A342" s="162" t="s">
         <v>115</v>
       </c>
@@ -23702,10 +23709,10 @@
       <c r="J351" s="31"/>
       <c r="K351" s="32"/>
       <c r="L351" s="33">
-        <v>3392.78</v>
-      </c>
-      <c r="M351" s="33">
-        <v>16.920000000000002</v>
+        <v>3433</v>
+      </c>
+      <c r="M351" s="186">
+        <v>16.29</v>
       </c>
       <c r="N351" s="34"/>
       <c r="O351" s="34"/>
@@ -24423,7 +24430,7 @@
         <v>3.2386363636363602E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" s="97" t="s">
         <v>115</v>
       </c>
@@ -24496,7 +24503,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" s="97" t="s">
         <v>115</v>
       </c>
@@ -24563,7 +24570,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="366" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" s="97" t="s">
         <v>115</v>
       </c>
@@ -24630,7 +24637,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="367" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" s="97" t="s">
         <v>115</v>
       </c>
@@ -24680,7 +24687,7 @@
         <v>5.0017045454545439E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" s="97" t="s">
         <v>115</v>
       </c>
@@ -24747,7 +24754,7 @@
       <c r="AC368" s="61"/>
       <c r="AD368" s="29"/>
     </row>
-    <row r="369" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369" s="97" t="s">
         <v>115</v>
       </c>
@@ -24809,7 +24816,7 @@
       <c r="AC369" s="61"/>
       <c r="AD369" s="29"/>
     </row>
-    <row r="370" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" s="97" t="s">
         <v>115</v>
       </c>
@@ -24869,7 +24876,7 @@
       <c r="AC370" s="9"/>
       <c r="AD370" s="29"/>
     </row>
-    <row r="371" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" s="97" t="s">
         <v>115</v>
       </c>
@@ -24911,7 +24918,7 @@
       <c r="AC371" s="9"/>
       <c r="AD371" s="29"/>
     </row>
-    <row r="372" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" s="97" t="s">
         <v>115</v>
       </c>
@@ -24967,7 +24974,7 @@
       </c>
       <c r="AF372" s="32"/>
     </row>
-    <row r="373" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373" s="97" t="s">
         <v>115</v>
       </c>
@@ -25011,7 +25018,7 @@
       <c r="AB373" s="9"/>
       <c r="AC373" s="9"/>
     </row>
-    <row r="374" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" s="97" t="s">
         <v>115</v>
       </c>
@@ -25073,7 +25080,7 @@
       <c r="AB374" s="9"/>
       <c r="AC374" s="9"/>
     </row>
-    <row r="375" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A375" s="97" t="s">
         <v>115</v>
       </c>
@@ -25138,7 +25145,7 @@
       <c r="AB375" s="9"/>
       <c r="AC375" s="9"/>
     </row>
-    <row r="376" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" s="97" t="s">
         <v>115</v>
       </c>
@@ -25196,7 +25203,7 @@
       <c r="AC376" s="20"/>
       <c r="AD376" s="21"/>
     </row>
-    <row r="377" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" s="97" t="s">
         <v>115</v>
       </c>
@@ -25239,7 +25246,7 @@
       <c r="AB377" s="9"/>
       <c r="AC377" s="9"/>
     </row>
-    <row r="378" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A378" s="97" t="s">
         <v>115</v>
       </c>
@@ -25313,7 +25320,7 @@
         <v>5.0017045454545439E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379" s="97" t="s">
         <v>115</v>
       </c>
@@ -25386,7 +25393,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="380" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A380" s="97" t="s">
         <v>115</v>
       </c>
@@ -25464,7 +25471,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="381" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A381" s="97" t="s">
         <v>115</v>
       </c>
@@ -25538,7 +25545,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="382" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A382" s="97" t="s">
         <v>115</v>
       </c>
@@ -25588,7 +25595,7 @@
         <v>5.7299999999999962E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A383" s="97" t="s">
         <v>115</v>
       </c>
@@ -25659,7 +25666,7 @@
       <c r="AC383" s="61"/>
       <c r="AD383" s="29"/>
     </row>
-    <row r="384" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A384" s="97" t="s">
         <v>115</v>
       </c>
@@ -25722,7 +25729,7 @@
       <c r="AC384" s="9"/>
       <c r="AD384" s="29"/>
     </row>
-    <row r="385" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A385" s="97" t="s">
         <v>115</v>
       </c>
@@ -25766,7 +25773,7 @@
       <c r="AC385" s="9"/>
       <c r="AD385" s="29"/>
     </row>
-    <row r="386" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A386" s="97" t="s">
         <v>115</v>
       </c>
@@ -25822,7 +25829,7 @@
       </c>
       <c r="AF386" s="32"/>
     </row>
-    <row r="387" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A387" s="97" t="s">
         <v>115</v>
       </c>
@@ -25866,7 +25873,7 @@
       <c r="AB387" s="9"/>
       <c r="AC387" s="9"/>
     </row>
-    <row r="388" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A388" s="97" t="s">
         <v>115</v>
       </c>
@@ -25928,7 +25935,7 @@
       <c r="AB388" s="9"/>
       <c r="AC388" s="9"/>
     </row>
-    <row r="389" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A389" s="97" t="s">
         <v>115</v>
       </c>
@@ -25976,7 +25983,7 @@
       <c r="AB389" s="9"/>
       <c r="AC389" s="9"/>
     </row>
-    <row r="390" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A390" s="97" t="s">
         <v>115</v>
       </c>
@@ -26038,7 +26045,7 @@
       <c r="AB390" s="9"/>
       <c r="AC390" s="9"/>
     </row>
-    <row r="391" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A391" s="97" t="s">
         <v>115</v>
       </c>
@@ -26082,7 +26089,7 @@
       <c r="AC391" s="20"/>
       <c r="AD391" s="21"/>
     </row>
-    <row r="392" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A392" s="97" t="s">
         <v>115</v>
       </c>
@@ -26156,7 +26163,7 @@
         <v>5.7300000000000018E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A393" s="97" t="s">
         <v>115</v>
       </c>
@@ -26229,7 +26236,7 @@
         <v>6.54E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394" s="97" t="s">
         <v>115</v>
       </c>
@@ -26302,7 +26309,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="395" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A395" s="97" t="s">
         <v>115</v>
       </c>
@@ -26366,7 +26373,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="396" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A396" s="97" t="s">
         <v>115</v>
       </c>
@@ -26437,7 +26444,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="397" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397" s="97" t="s">
         <v>115</v>
       </c>
@@ -26513,7 +26520,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="398" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A398" s="97" t="s">
         <v>115</v>
       </c>
@@ -26568,7 +26575,7 @@
       <c r="AC398" s="61"/>
       <c r="AD398" s="29"/>
     </row>
-    <row r="399" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399" s="97" t="s">
         <v>115</v>
       </c>
@@ -26630,7 +26637,7 @@
       <c r="AC399" s="61"/>
       <c r="AD399" s="29"/>
     </row>
-    <row r="400" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A400" s="97" t="s">
         <v>115</v>
       </c>
@@ -26692,7 +26699,7 @@
       <c r="AC400" s="9"/>
       <c r="AD400" s="29"/>
     </row>
-    <row r="401" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A401" s="97" t="s">
         <v>115</v>
       </c>
@@ -26736,7 +26743,7 @@
       <c r="AC401" s="9"/>
       <c r="AD401" s="29"/>
     </row>
-    <row r="402" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402" s="97" t="s">
         <v>115</v>
       </c>
@@ -26792,7 +26799,7 @@
       </c>
       <c r="AF402" s="32"/>
     </row>
-    <row r="403" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A403" s="97" t="s">
         <v>115</v>
       </c>
@@ -26836,7 +26843,7 @@
       <c r="AB403" s="9"/>
       <c r="AC403" s="9"/>
     </row>
-    <row r="404" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404" s="97" t="s">
         <v>115</v>
       </c>
@@ -26898,7 +26905,7 @@
       <c r="AB404" s="9"/>
       <c r="AC404" s="9"/>
     </row>
-    <row r="405" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405" s="97" t="s">
         <v>115</v>
       </c>
@@ -26961,7 +26968,7 @@
       <c r="AB405" s="9"/>
       <c r="AC405" s="9"/>
     </row>
-    <row r="406" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A406" s="97" t="s">
         <v>115</v>
       </c>
@@ -27018,7 +27025,7 @@
       <c r="AB406" s="9"/>
       <c r="AC406" s="9"/>
     </row>
-    <row r="407" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407" s="97" t="s">
         <v>115</v>
       </c>
@@ -27061,7 +27068,7 @@
       <c r="AB407" s="9"/>
       <c r="AC407" s="9"/>
     </row>
-    <row r="408" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408" s="184" t="s">
         <v>115</v>
       </c>
@@ -27135,7 +27142,7 @@
         <v>3.7732954545454445E-2</v>
       </c>
     </row>
-    <row r="409" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A409" s="97" t="s">
         <v>115</v>
       </c>
@@ -27208,7 +27215,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="410" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A410" s="97" t="s">
         <v>115</v>
       </c>
@@ -27281,7 +27288,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="411" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411" s="97" t="s">
         <v>115</v>
       </c>
@@ -27345,7 +27352,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="412" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412" s="97" t="s">
         <v>115</v>
       </c>
@@ -27416,7 +27423,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="413" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A413" s="97" t="s">
         <v>115</v>
       </c>
@@ -27492,7 +27499,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="414" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A414" s="97" t="s">
         <v>115</v>
       </c>
@@ -27547,7 +27554,7 @@
       <c r="AC414" s="61"/>
       <c r="AD414" s="29"/>
     </row>
-    <row r="415" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A415" s="97" t="s">
         <v>115</v>
       </c>
@@ -27609,7 +27616,7 @@
       <c r="AC415" s="61"/>
       <c r="AD415" s="29"/>
     </row>
-    <row r="416" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A416" s="97" t="s">
         <v>115</v>
       </c>
@@ -27671,7 +27678,7 @@
       <c r="AC416" s="9"/>
       <c r="AD416" s="29"/>
     </row>
-    <row r="417" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A417" s="97" t="s">
         <v>115</v>
       </c>
@@ -27715,7 +27722,7 @@
       <c r="AC417" s="9"/>
       <c r="AD417" s="29"/>
     </row>
-    <row r="418" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A418" s="97" t="s">
         <v>115</v>
       </c>
@@ -27767,7 +27774,7 @@
       </c>
       <c r="AF418" s="32"/>
     </row>
-    <row r="419" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A419" s="97" t="s">
         <v>115</v>
       </c>
@@ -27811,7 +27818,7 @@
       <c r="AB419" s="9"/>
       <c r="AC419" s="9"/>
     </row>
-    <row r="420" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A420" s="97" t="s">
         <v>115</v>
       </c>
@@ -27873,7 +27880,7 @@
       <c r="AB420" s="9"/>
       <c r="AC420" s="9"/>
     </row>
-    <row r="421" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A421" s="97" t="s">
         <v>115</v>
       </c>
@@ -27936,7 +27943,7 @@
       <c r="AB421" s="9"/>
       <c r="AC421" s="9"/>
     </row>
-    <row r="422" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A422" s="97" t="s">
         <v>115</v>
       </c>
@@ -27993,7 +28000,7 @@
       <c r="AB422" s="9"/>
       <c r="AC422" s="9"/>
     </row>
-    <row r="423" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A423" s="97" t="s">
         <v>115</v>
       </c>
@@ -28036,7 +28043,7 @@
       <c r="AB423" s="9"/>
       <c r="AC423" s="9"/>
     </row>
-    <row r="424" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A424" s="97" t="s">
         <v>115</v>
       </c>
@@ -28110,7 +28117,7 @@
         <v>3.7732954545454556E-2</v>
       </c>
     </row>
-    <row r="425" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A425" s="97" t="s">
         <v>115</v>
       </c>
@@ -28183,7 +28190,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="426" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A426" s="97" t="s">
         <v>115</v>
       </c>
@@ -28256,7 +28263,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="427" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A427" s="97" t="s">
         <v>115</v>
       </c>
@@ -28323,7 +28330,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="428" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A428" s="97"/>
       <c r="B428" s="49"/>
       <c r="C428" s="5"/>
@@ -28363,7 +28370,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="429" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A429" s="97" t="s">
         <v>115</v>
       </c>
@@ -28429,7 +28436,7 @@
       <c r="AB429" s="18"/>
       <c r="AD429" s="19"/>
     </row>
-    <row r="430" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A430" s="97" t="s">
         <v>115</v>
       </c>
@@ -28476,7 +28483,7 @@
       <c r="AB430" s="18"/>
       <c r="AD430" s="19"/>
     </row>
-    <row r="431" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A431" s="97"/>
       <c r="B431" s="49"/>
       <c r="C431" s="5"/>
@@ -28505,7 +28512,7 @@
       <c r="AB431" s="18"/>
       <c r="AD431" s="19"/>
     </row>
-    <row r="432" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A432" s="97" t="s">
         <v>115</v>
       </c>
@@ -28534,7 +28541,7 @@
       <c r="AB432" s="18"/>
       <c r="AD432" s="19"/>
     </row>
-    <row r="433" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A433" s="97" t="s">
         <v>115</v>
       </c>
@@ -28578,7 +28585,7 @@
       <c r="AC433" s="9"/>
       <c r="AD433" s="29"/>
     </row>
-    <row r="434" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A434" s="97" t="s">
         <v>115</v>
       </c>
@@ -28630,7 +28637,7 @@
       </c>
       <c r="AF434" s="32"/>
     </row>
-    <row r="435" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A435" s="97" t="s">
         <v>115</v>
       </c>
@@ -28674,7 +28681,7 @@
       <c r="AB435" s="9"/>
       <c r="AC435" s="9"/>
     </row>
-    <row r="436" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A436" s="97" t="s">
         <v>115</v>
       </c>
@@ -28721,7 +28728,7 @@
       <c r="AB436" s="9"/>
       <c r="AC436" s="9"/>
     </row>
-    <row r="437" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A437" s="97" t="s">
         <v>115</v>
       </c>
@@ -28765,7 +28772,7 @@
       <c r="AB437" s="9"/>
       <c r="AC437" s="9"/>
     </row>
-    <row r="438" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A438" s="97" t="s">
         <v>115</v>
       </c>
@@ -28799,7 +28806,7 @@
       <c r="AB438" s="18"/>
       <c r="AD438" s="19"/>
     </row>
-    <row r="439" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A439" s="97" t="s">
         <v>115</v>
       </c>
@@ -28828,7 +28835,7 @@
       <c r="AB439" s="18"/>
       <c r="AD439" s="19"/>
     </row>
-    <row r="440" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A440" s="97" t="s">
         <v>115</v>
       </c>
@@ -28902,7 +28909,7 @@
         <v>3.8238095238095293E-2</v>
       </c>
     </row>
-    <row r="441" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A441" s="97" t="s">
         <v>115</v>
       </c>
@@ -28975,7 +28982,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="442" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A442" s="97" t="s">
         <v>115</v>
       </c>
@@ -29004,7 +29011,7 @@
       <c r="AB442" s="18"/>
       <c r="AD442" s="19"/>
     </row>
-    <row r="443" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A443" s="97" t="s">
         <v>115</v>
       </c>
@@ -29033,7 +29040,7 @@
       <c r="AB443" s="18"/>
       <c r="AD443" s="19"/>
     </row>
-    <row r="444" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A444" s="97"/>
       <c r="B444" s="49"/>
       <c r="C444" s="5"/>
@@ -29047,7 +29054,7 @@
       <c r="AB444" s="18"/>
       <c r="AD444" s="19"/>
     </row>
-    <row r="445" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A445" s="97" t="s">
         <v>115</v>
       </c>
@@ -29076,7 +29083,7 @@
       <c r="AB445" s="18"/>
       <c r="AD445" s="19"/>
     </row>
-    <row r="446" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A446" s="97" t="s">
         <v>115</v>
       </c>
@@ -29105,7 +29112,7 @@
       <c r="AB446" s="18"/>
       <c r="AD446" s="19"/>
     </row>
-    <row r="447" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A447" s="97" t="s">
         <v>115</v>
       </c>
@@ -29134,7 +29141,7 @@
       <c r="AB447" s="18"/>
       <c r="AD447" s="19"/>
     </row>
-    <row r="448" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A448" s="97" t="s">
         <v>115</v>
       </c>
@@ -29163,7 +29170,7 @@
       <c r="AB448" s="18"/>
       <c r="AD448" s="19"/>
     </row>
-    <row r="449" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449" s="97" t="s">
         <v>115</v>
       </c>
@@ -29207,7 +29214,7 @@
       <c r="AC449" s="9"/>
       <c r="AD449" s="29"/>
     </row>
-    <row r="450" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" s="97" t="s">
         <v>115</v>
       </c>
@@ -29259,7 +29266,7 @@
       </c>
       <c r="AF450" s="32"/>
     </row>
-    <row r="451" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451" s="97" t="s">
         <v>115</v>
       </c>
@@ -29303,7 +29310,7 @@
       <c r="AB451" s="9"/>
       <c r="AC451" s="9"/>
     </row>
-    <row r="452" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452" s="97" t="s">
         <v>115</v>
       </c>
@@ -29332,7 +29339,7 @@
       <c r="AB452" s="18"/>
       <c r="AD452" s="19"/>
     </row>
-    <row r="453" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A453" s="97" t="s">
         <v>115</v>
       </c>
@@ -29361,7 +29368,7 @@
       <c r="AB453" s="18"/>
       <c r="AD453" s="19"/>
     </row>
-    <row r="454" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" s="97" t="s">
         <v>115</v>
       </c>

--- a/sinchi metals assays over time.xlsx
+++ b/sinchi metals assays over time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\claude\SMPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E0387D-6212-4C6C-A810-833A71F7D972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2490F6E-F7CA-49AE-9A43-8F1FF131DB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{786040CA-C117-4D0F-BDFA-1AE45497D150}"/>
+    <workbookView xWindow="19890" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{786040CA-C117-4D0F-BDFA-1AE45497D150}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="358">
   <si>
     <t>Sell Ref</t>
   </si>
@@ -1826,13 +1826,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1FF62F3F-9C45-4981-80CA-DD7D85DCFAA1}" name="Table1" displayName="Table1" ref="A1:AD454" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9">
-  <autoFilter ref="A1:AD454" xr:uid="{1FF62F3F-9C45-4981-80CA-DD7D85DCFAA1}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="93302"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AD454" xr:uid="{1FF62F3F-9C45-4981-80CA-DD7D85DCFAA1}"/>
   <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{7F78213E-9C1A-4957-BB0D-8340CDD31563}" name="Open/Close" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{1B46E019-1EBF-46CE-9BBA-1DC43C21DA3F}" name="P/S" dataDxfId="7"/>
@@ -2317,7 +2311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" s="48" t="s">
         <v>57</v>
       </c>
@@ -2386,7 +2380,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="3" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" s="48" t="s">
         <v>57</v>
       </c>
@@ -2447,7 +2441,7 @@
         <v>3.0599999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" s="48" t="s">
         <v>57</v>
       </c>
@@ -2520,7 +2514,7 @@
         <v>2.46E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" s="48" t="s">
         <v>57</v>
       </c>
@@ -2575,7 +2569,7 @@
       <c r="AC5" s="62"/>
       <c r="AD5" s="29"/>
     </row>
-    <row r="6" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" s="48" t="s">
         <v>57</v>
       </c>
@@ -2647,7 +2641,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" s="48" t="s">
         <v>57</v>
       </c>
@@ -2712,7 +2706,7 @@
       <c r="AB7" s="9"/>
       <c r="AC7" s="9"/>
     </row>
-    <row r="8" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" s="48" t="s">
         <v>57</v>
       </c>
@@ -2778,7 +2772,7 @@
       <c r="AC8" s="9"/>
       <c r="AD8" s="29"/>
     </row>
-    <row r="9" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" s="48" t="s">
         <v>57</v>
       </c>
@@ -2846,7 +2840,7 @@
         <v>2.2754545454545472E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" s="48" t="s">
         <v>57</v>
       </c>
@@ -2915,7 +2909,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A11" s="48" t="s">
         <v>57</v>
       </c>
@@ -2991,7 +2985,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A12" s="48" t="s">
         <v>57</v>
       </c>
@@ -3054,7 +3048,7 @@
       <c r="AC12" s="61"/>
       <c r="AD12" s="29"/>
     </row>
-    <row r="13" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A13" s="48" t="s">
         <v>57</v>
       </c>
@@ -3119,7 +3113,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
     </row>
-    <row r="14" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A14" s="48" t="s">
         <v>57</v>
       </c>
@@ -3184,7 +3178,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
     </row>
-    <row r="15" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A15" s="48" t="s">
         <v>57</v>
       </c>
@@ -3252,7 +3246,7 @@
         <v>3.6266233766233835E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A16" s="48" t="s">
         <v>57</v>
       </c>
@@ -3321,7 +3315,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A17" s="48" t="s">
         <v>57</v>
       </c>
@@ -3394,7 +3388,7 @@
         <v>2.2100000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A18" s="48" t="s">
         <v>57</v>
       </c>
@@ -3466,7 +3460,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A19" s="48" t="s">
         <v>57</v>
       </c>
@@ -3530,7 +3524,7 @@
       <c r="AE19" s="80"/>
       <c r="AF19" s="80"/>
     </row>
-    <row r="20" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A20" s="48" t="s">
         <v>57</v>
       </c>
@@ -3587,7 +3581,7 @@
       <c r="AE20" s="80"/>
       <c r="AF20" s="80"/>
     </row>
-    <row r="21" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A21" s="48" t="s">
         <v>57</v>
       </c>
@@ -3657,7 +3651,7 @@
       <c r="AE21" s="80"/>
       <c r="AF21" s="80"/>
     </row>
-    <row r="22" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A22" s="48" t="s">
         <v>57</v>
       </c>
@@ -3726,7 +3720,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A23" s="48" t="s">
         <v>57</v>
       </c>
@@ -3796,7 +3790,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A24" s="48" t="s">
         <v>57</v>
       </c>
@@ -3851,7 +3845,7 @@
       <c r="AC24" s="61"/>
       <c r="AD24" s="29"/>
     </row>
-    <row r="25" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A25" s="48" t="s">
         <v>57</v>
       </c>
@@ -3900,7 +3894,7 @@
       <c r="AC25" s="61"/>
       <c r="AD25" s="29"/>
     </row>
-    <row r="26" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A26" s="48" t="s">
         <v>57</v>
       </c>
@@ -3954,7 +3948,7 @@
       <c r="AC26" s="61"/>
       <c r="AD26" s="29"/>
     </row>
-    <row r="27" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A27" s="48" t="s">
         <v>57</v>
       </c>
@@ -4017,7 +4011,7 @@
       <c r="AC27" s="9"/>
       <c r="AD27" s="29"/>
     </row>
-    <row r="28" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A28" s="48" t="s">
         <v>57</v>
       </c>
@@ -4062,7 +4056,7 @@
       <c r="AC28" s="9"/>
       <c r="AD28" s="29"/>
     </row>
-    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A29" s="48" t="s">
         <v>57</v>
       </c>
@@ -4106,7 +4100,7 @@
       <c r="AB29" s="9"/>
       <c r="AC29" s="9"/>
     </row>
-    <row r="30" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A30" s="48" t="s">
         <v>57</v>
       </c>
@@ -4150,7 +4144,7 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
     </row>
-    <row r="31" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A31" s="48" t="s">
         <v>57</v>
       </c>
@@ -4215,7 +4209,7 @@
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
     </row>
-    <row r="32" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A32" s="48" t="s">
         <v>57</v>
       </c>
@@ -4280,7 +4274,7 @@
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
     </row>
-    <row r="33" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A33" s="48" t="s">
         <v>57</v>
       </c>
@@ -4348,7 +4342,7 @@
         <v>1.9734848484848411E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A34" s="48" t="s">
         <v>57</v>
       </c>
@@ -4417,7 +4411,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="35" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A35" s="48" t="s">
         <v>57</v>
       </c>
@@ -4481,7 +4475,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A36" s="48" t="s">
         <v>57</v>
       </c>
@@ -4536,7 +4530,7 @@
       <c r="AC36" s="62"/>
       <c r="AD36" s="29"/>
     </row>
-    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A37" s="48" t="s">
         <v>57</v>
       </c>
@@ -4597,7 +4591,7 @@
       <c r="AC37" s="61"/>
       <c r="AD37" s="29"/>
     </row>
-    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A38" s="48" t="s">
         <v>57</v>
       </c>
@@ -4666,7 +4660,7 @@
       <c r="AC38" s="61"/>
       <c r="AD38" s="29"/>
     </row>
-    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A39" s="48" t="s">
         <v>57</v>
       </c>
@@ -4731,7 +4725,7 @@
       <c r="AC39" s="9"/>
       <c r="AD39" s="29"/>
     </row>
-    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A40" s="48" t="s">
         <v>57</v>
       </c>
@@ -4796,7 +4790,7 @@
       <c r="AC40" s="9"/>
       <c r="AD40" s="29"/>
     </row>
-    <row r="41" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A41" s="48" t="s">
         <v>57</v>
       </c>
@@ -4853,7 +4847,7 @@
       </c>
       <c r="AD41" s="29"/>
     </row>
-    <row r="42" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A42" s="48" t="s">
         <v>57</v>
       </c>
@@ -4910,7 +4904,7 @@
       </c>
       <c r="AD42" s="29"/>
     </row>
-    <row r="43" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A43" s="48" t="s">
         <v>57</v>
       </c>
@@ -4968,7 +4962,7 @@
       </c>
       <c r="AD43" s="21"/>
     </row>
-    <row r="44" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A44" s="48" t="s">
         <v>57</v>
       </c>
@@ -5012,7 +5006,7 @@
       <c r="AB44" s="9"/>
       <c r="AC44" s="9"/>
     </row>
-    <row r="45" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A45" s="48" t="s">
         <v>57</v>
       </c>
@@ -5077,7 +5071,7 @@
       <c r="AB45" s="9"/>
       <c r="AC45" s="9"/>
     </row>
-    <row r="46" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A46" s="48" t="s">
         <v>57</v>
       </c>
@@ -5132,7 +5126,7 @@
       <c r="AB46" s="9"/>
       <c r="AC46" s="9"/>
     </row>
-    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A47" s="48" t="s">
         <v>57</v>
       </c>
@@ -5204,7 +5198,7 @@
         <v>1.6590909090909101E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A48" s="48" t="s">
         <v>57</v>
       </c>
@@ -5273,7 +5267,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A49" s="48" t="s">
         <v>57</v>
       </c>
@@ -5337,7 +5331,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A50" s="48" t="s">
         <v>57</v>
       </c>
@@ -5392,7 +5386,7 @@
       <c r="AC50" s="62"/>
       <c r="AD50" s="29"/>
     </row>
-    <row r="51" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A51" s="48" t="s">
         <v>57</v>
       </c>
@@ -5455,7 +5449,7 @@
       <c r="AC51" s="62"/>
       <c r="AD51" s="29"/>
     </row>
-    <row r="52" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A52" s="48" t="s">
         <v>57</v>
       </c>
@@ -5520,7 +5514,7 @@
       </c>
       <c r="AD52" s="29"/>
     </row>
-    <row r="53" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A53" s="48" t="s">
         <v>57</v>
       </c>
@@ -5585,7 +5579,7 @@
       </c>
       <c r="AD53" s="29"/>
     </row>
-    <row r="54" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A54" s="48" t="s">
         <v>57</v>
       </c>
@@ -5671,7 +5665,7 @@
       </c>
       <c r="AD54" s="91"/>
     </row>
-    <row r="55" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A55" s="48" t="s">
         <v>57</v>
       </c>
@@ -5738,7 +5732,7 @@
       <c r="AC55" s="62"/>
       <c r="AD55" s="29"/>
     </row>
-    <row r="56" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A56" s="48" t="s">
         <v>57</v>
       </c>
@@ -5801,7 +5795,7 @@
       <c r="AC56" s="62"/>
       <c r="AD56" s="29"/>
     </row>
-    <row r="57" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A57" s="48" t="s">
         <v>57</v>
       </c>
@@ -5858,7 +5852,7 @@
       </c>
       <c r="AD57" s="29"/>
     </row>
-    <row r="58" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A58" s="48" t="s">
         <v>57</v>
       </c>
@@ -5915,7 +5909,7 @@
       </c>
       <c r="AD58" s="29"/>
     </row>
-    <row r="59" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A59" s="48" t="s">
         <v>57</v>
       </c>
@@ -5975,7 +5969,7 @@
       </c>
       <c r="AD59" s="21"/>
     </row>
-    <row r="60" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A60" s="48" t="s">
         <v>57</v>
       </c>
@@ -6040,7 +6034,7 @@
       <c r="AB60" s="9"/>
       <c r="AC60" s="9"/>
     </row>
-    <row r="61" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A61" s="48" t="s">
         <v>57</v>
       </c>
@@ -6095,7 +6089,7 @@
       <c r="AB61" s="9"/>
       <c r="AC61" s="9"/>
     </row>
-    <row r="62" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A62" s="48" t="s">
         <v>57</v>
       </c>
@@ -6179,7 +6173,7 @@
         <v>1.6405303030303076E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A63" s="48" t="s">
         <v>57</v>
       </c>
@@ -6248,7 +6242,7 @@
         <v>1.01E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A64" s="48" t="s">
         <v>57</v>
       </c>
@@ -6320,7 +6314,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A65" s="48" t="s">
         <v>57</v>
       </c>
@@ -6387,7 +6381,7 @@
       <c r="AC65" s="61"/>
       <c r="AD65" s="29"/>
     </row>
-    <row r="66" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A66" s="48" t="s">
         <v>57</v>
       </c>
@@ -6443,7 +6437,7 @@
       </c>
       <c r="AD66" s="29"/>
     </row>
-    <row r="67" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A67" s="48" t="s">
         <v>57</v>
       </c>
@@ -6499,7 +6493,7 @@
       </c>
       <c r="AD67" s="29"/>
     </row>
-    <row r="68" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A68" s="48" t="s">
         <v>57</v>
       </c>
@@ -6557,7 +6551,7 @@
       </c>
       <c r="AD68" s="91"/>
     </row>
-    <row r="69" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A69" s="48" t="s">
         <v>57</v>
       </c>
@@ -6620,7 +6614,7 @@
       <c r="AC69" s="9"/>
       <c r="AD69" s="29"/>
     </row>
-    <row r="70" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A70" s="48" t="s">
         <v>57</v>
       </c>
@@ -6664,7 +6658,7 @@
       <c r="AB70" s="9"/>
       <c r="AC70" s="9"/>
     </row>
-    <row r="71" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A71" s="48" t="s">
         <v>57</v>
       </c>
@@ -6708,7 +6702,7 @@
       <c r="AB71" s="9"/>
       <c r="AC71" s="9"/>
     </row>
-    <row r="72" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A72" s="48" t="s">
         <v>57</v>
       </c>
@@ -6767,7 +6761,7 @@
         <v>152.27699999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A73" s="48" t="s">
         <v>57</v>
       </c>
@@ -6824,7 +6818,7 @@
       <c r="AB73" s="9"/>
       <c r="AC73" s="9"/>
     </row>
-    <row r="74" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A74" s="48" t="s">
         <v>57</v>
       </c>
@@ -6883,7 +6877,7 @@
         <v>152.32499999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A75" s="48" t="s">
         <v>57</v>
       </c>
@@ -6940,7 +6934,7 @@
       <c r="AB75" s="9"/>
       <c r="AC75" s="9"/>
     </row>
-    <row r="76" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A76" s="48" t="s">
         <v>57</v>
       </c>
@@ -6997,7 +6991,7 @@
       <c r="AB76" s="20"/>
       <c r="AC76" s="20"/>
     </row>
-    <row r="77" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A77" s="48" t="s">
         <v>57</v>
       </c>
@@ -7056,7 +7050,7 @@
         <v>304.60199999999998</v>
       </c>
     </row>
-    <row r="78" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A78" s="48" t="s">
         <v>57</v>
       </c>
@@ -7113,7 +7107,7 @@
       <c r="AB78" s="9"/>
       <c r="AC78" s="9"/>
     </row>
-    <row r="79" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A79" s="48" t="s">
         <v>57</v>
       </c>
@@ -7156,7 +7150,7 @@
       <c r="AB79" s="9"/>
       <c r="AC79" s="9"/>
     </row>
-    <row r="80" spans="1:30" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A80" s="48" t="s">
         <v>57</v>
       </c>
@@ -7228,7 +7222,7 @@
         <v>1.103246753246756E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A81" s="97" t="s">
         <v>115</v>
       </c>
@@ -7297,7 +7291,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="82" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A82" s="97" t="s">
         <v>115</v>
       </c>
@@ -7379,7 +7373,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="83" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A83" s="97" t="s">
         <v>115</v>
       </c>
@@ -7436,7 +7430,7 @@
       </c>
       <c r="AD83" s="29"/>
     </row>
-    <row r="84" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A84" s="97" t="s">
         <v>115</v>
       </c>
@@ -7492,7 +7486,7 @@
       </c>
       <c r="AD84" s="29"/>
     </row>
-    <row r="85" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A85" s="97" t="s">
         <v>115</v>
       </c>
@@ -7550,7 +7544,7 @@
       </c>
       <c r="AD85" s="91"/>
     </row>
-    <row r="86" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A86" s="97" t="s">
         <v>115</v>
       </c>
@@ -7604,7 +7598,7 @@
       <c r="AC86" s="61"/>
       <c r="AD86" s="29"/>
     </row>
-    <row r="87" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A87" s="97" t="s">
         <v>115</v>
       </c>
@@ -7649,7 +7643,7 @@
       <c r="AC87" s="9"/>
       <c r="AD87" s="29"/>
     </row>
-    <row r="88" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A88" s="97" t="s">
         <v>115</v>
       </c>
@@ -7693,7 +7687,7 @@
       <c r="AB88" s="9"/>
       <c r="AC88" s="9"/>
     </row>
-    <row r="89" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A89" s="97" t="s">
         <v>115</v>
       </c>
@@ -7737,7 +7731,7 @@
       <c r="AB89" s="9"/>
       <c r="AC89" s="9"/>
     </row>
-    <row r="90" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A90" s="97" t="s">
         <v>115</v>
       </c>
@@ -7780,7 +7774,7 @@
       <c r="AB90" s="9"/>
       <c r="AC90" s="9"/>
     </row>
-    <row r="91" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A91" s="97" t="s">
         <v>115</v>
       </c>
@@ -7823,7 +7817,7 @@
       <c r="AB91" s="9"/>
       <c r="AC91" s="9"/>
     </row>
-    <row r="92" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A92" s="97" t="s">
         <v>115</v>
       </c>
@@ -7866,7 +7860,7 @@
       <c r="AB92" s="9"/>
       <c r="AC92" s="9"/>
     </row>
-    <row r="93" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A93" s="97" t="s">
         <v>115</v>
       </c>
@@ -7909,7 +7903,7 @@
       <c r="AB93" s="9"/>
       <c r="AC93" s="9"/>
     </row>
-    <row r="94" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A94" s="97" t="s">
         <v>115</v>
       </c>
@@ -7967,7 +7961,7 @@
       <c r="AC94" s="20"/>
       <c r="AD94" s="21"/>
     </row>
-    <row r="95" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A95" s="97" t="s">
         <v>115</v>
       </c>
@@ -8025,7 +8019,7 @@
       <c r="AC95" s="20"/>
       <c r="AD95" s="21"/>
     </row>
-    <row r="96" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A96" s="97" t="s">
         <v>115</v>
       </c>
@@ -8082,7 +8076,7 @@
       <c r="AB96" s="9"/>
       <c r="AC96" s="9"/>
     </row>
-    <row r="97" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A97" s="97" t="s">
         <v>115</v>
       </c>
@@ -8125,7 +8119,7 @@
       <c r="AB97" s="9"/>
       <c r="AC97" s="9"/>
     </row>
-    <row r="98" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A98" s="97" t="s">
         <v>115</v>
       </c>
@@ -8201,7 +8195,7 @@
         <v>1.6977272727272674E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A99" s="97" t="s">
         <v>115</v>
       </c>
@@ -8276,7 +8270,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="100" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A100" s="97" t="s">
         <v>115</v>
       </c>
@@ -8356,7 +8350,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A101" s="97" t="s">
         <v>115</v>
       </c>
@@ -8419,7 +8413,7 @@
       <c r="AC101" s="61"/>
       <c r="AD101" s="29"/>
     </row>
-    <row r="102" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A102" s="97" t="s">
         <v>115</v>
       </c>
@@ -8461,7 +8455,7 @@
       <c r="AB102" s="9"/>
       <c r="AC102" s="9"/>
     </row>
-    <row r="103" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A103" s="97" t="s">
         <v>115</v>
       </c>
@@ -8523,7 +8517,7 @@
       <c r="AB103" s="9"/>
       <c r="AC103" s="9"/>
     </row>
-    <row r="104" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A104" s="97" t="s">
         <v>115</v>
       </c>
@@ -8586,7 +8580,7 @@
       <c r="AB104" s="9"/>
       <c r="AC104" s="9"/>
     </row>
-    <row r="105" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A105" s="97" t="s">
         <v>115</v>
       </c>
@@ -8662,7 +8656,7 @@
         <v>1.2202020202019992E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A106" s="97" t="s">
         <v>115</v>
       </c>
@@ -8737,7 +8731,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="107" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A107" s="97" t="s">
         <v>115</v>
       </c>
@@ -8817,7 +8811,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A108" s="97" t="s">
         <v>115</v>
       </c>
@@ -8880,7 +8874,7 @@
       <c r="AC108" s="61"/>
       <c r="AD108" s="29"/>
     </row>
-    <row r="109" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A109" s="97" t="s">
         <v>115</v>
       </c>
@@ -8922,7 +8916,7 @@
       <c r="AC109" s="61"/>
       <c r="AD109" s="29"/>
     </row>
-    <row r="110" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A110" s="97" t="s">
         <v>115</v>
       </c>
@@ -8964,7 +8958,7 @@
       <c r="AC110" s="61"/>
       <c r="AD110" s="29"/>
     </row>
-    <row r="111" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A111" s="97" t="s">
         <v>115</v>
       </c>
@@ -9006,7 +9000,7 @@
       <c r="AC111" s="61"/>
       <c r="AD111" s="29"/>
     </row>
-    <row r="112" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A112" s="97" t="s">
         <v>115</v>
       </c>
@@ -9049,7 +9043,7 @@
       <c r="AC112" s="9"/>
       <c r="AD112" s="29"/>
     </row>
-    <row r="113" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A113" s="97" t="s">
         <v>115</v>
       </c>
@@ -9091,7 +9085,7 @@
       <c r="AB113" s="9"/>
       <c r="AC113" s="9"/>
     </row>
-    <row r="114" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A114" s="97" t="s">
         <v>115</v>
       </c>
@@ -9153,7 +9147,7 @@
       <c r="AB114" s="9"/>
       <c r="AC114" s="9"/>
     </row>
-    <row r="115" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A115" s="97" t="s">
         <v>115</v>
       </c>
@@ -9215,7 +9209,7 @@
       <c r="AB115" s="9"/>
       <c r="AC115" s="9"/>
     </row>
-    <row r="116" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A116" s="97" t="s">
         <v>115</v>
       </c>
@@ -9260,7 +9254,7 @@
       <c r="AB116" s="9"/>
       <c r="AC116" s="9"/>
     </row>
-    <row r="117" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A117" s="97" t="s">
         <v>115</v>
       </c>
@@ -9336,7 +9330,7 @@
         <v>1.1939393939394138E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A118" s="97" t="s">
         <v>115</v>
       </c>
@@ -9411,7 +9405,7 @@
         <v>2.3699999999999999E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A119" s="97" t="s">
         <v>115</v>
       </c>
@@ -9487,7 +9481,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="120" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A120" s="97" t="s">
         <v>115</v>
       </c>
@@ -9550,7 +9544,7 @@
       <c r="AC120" s="61"/>
       <c r="AD120" s="29"/>
     </row>
-    <row r="121" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A121" s="97" t="s">
         <v>115</v>
       </c>
@@ -9594,7 +9588,7 @@
       <c r="AC121" s="61"/>
       <c r="AD121" s="29"/>
     </row>
-    <row r="122" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A122" s="97" t="s">
         <v>115</v>
       </c>
@@ -9644,7 +9638,7 @@
       <c r="AC122" s="61"/>
       <c r="AD122" s="29"/>
     </row>
-    <row r="123" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A123" s="97" t="s">
         <v>115</v>
       </c>
@@ -9692,7 +9686,7 @@
       <c r="AC123" s="9"/>
       <c r="AD123" s="29"/>
     </row>
-    <row r="124" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A124" s="97" t="s">
         <v>115</v>
       </c>
@@ -9740,7 +9734,7 @@
       <c r="AC124" s="9"/>
       <c r="AD124" s="29"/>
     </row>
-    <row r="125" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A125" s="97" t="s">
         <v>115</v>
       </c>
@@ -9782,7 +9776,7 @@
       <c r="AB125" s="9"/>
       <c r="AC125" s="9"/>
     </row>
-    <row r="126" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A126" s="97" t="s">
         <v>115</v>
       </c>
@@ -9824,7 +9818,7 @@
       <c r="AB126" s="9"/>
       <c r="AC126" s="9"/>
     </row>
-    <row r="127" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A127" s="97" t="s">
         <v>115</v>
       </c>
@@ -9866,7 +9860,7 @@
       <c r="AB127" s="9"/>
       <c r="AC127" s="9"/>
     </row>
-    <row r="128" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A128" s="97" t="s">
         <v>115</v>
       </c>
@@ -9908,7 +9902,7 @@
       <c r="AB128" s="9"/>
       <c r="AC128" s="9"/>
     </row>
-    <row r="129" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A129" s="97" t="s">
         <v>115</v>
       </c>
@@ -9970,7 +9964,7 @@
       <c r="AB129" s="9"/>
       <c r="AC129" s="9"/>
     </row>
-    <row r="130" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A130" s="97" t="s">
         <v>115</v>
       </c>
@@ -10033,7 +10027,7 @@
       <c r="AB130" s="9"/>
       <c r="AC130" s="9"/>
     </row>
-    <row r="131" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A131" s="97" t="s">
         <v>115</v>
       </c>
@@ -10109,7 +10103,7 @@
         <v>1.6918831168831194E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A132" s="97" t="s">
         <v>115</v>
       </c>
@@ -10194,7 +10188,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A133" s="97" t="s">
         <v>115</v>
       </c>
@@ -10270,7 +10264,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="134" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A134" s="97" t="s">
         <v>115</v>
       </c>
@@ -10333,7 +10327,7 @@
       <c r="AC134" s="106"/>
       <c r="AD134" s="107"/>
     </row>
-    <row r="135" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A135" s="97" t="s">
         <v>115</v>
       </c>
@@ -10393,7 +10387,7 @@
       </c>
       <c r="AF135" s="32"/>
     </row>
-    <row r="136" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A136" s="97" t="s">
         <v>115</v>
       </c>
@@ -10458,7 +10452,7 @@
       <c r="AB136" s="9"/>
       <c r="AC136" s="9"/>
     </row>
-    <row r="137" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A137" s="97" t="s">
         <v>115</v>
       </c>
@@ -10533,7 +10527,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A138" s="97" t="s">
         <v>115</v>
       </c>
@@ -10619,7 +10613,7 @@
         <v>2.4196468990493547E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A139" s="97" t="s">
         <v>115</v>
       </c>
@@ -10688,7 +10682,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A140" s="97" t="s">
         <v>115</v>
       </c>
@@ -10758,7 +10752,7 @@
         <v>1.2800000000000001E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A141" s="97" t="s">
         <v>115</v>
       </c>
@@ -10832,7 +10826,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="142" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A142" s="97" t="s">
         <v>115</v>
       </c>
@@ -10889,7 +10883,7 @@
       </c>
       <c r="AD142" s="29"/>
     </row>
-    <row r="143" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A143" s="97" t="s">
         <v>115</v>
       </c>
@@ -10945,7 +10939,7 @@
       </c>
       <c r="AD143" s="29"/>
     </row>
-    <row r="144" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A144" s="97" t="s">
         <v>115</v>
       </c>
@@ -11001,7 +10995,7 @@
       </c>
       <c r="AD144" s="91"/>
     </row>
-    <row r="145" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A145" s="97" t="s">
         <v>115</v>
       </c>
@@ -11057,7 +11051,7 @@
       </c>
       <c r="AD145" s="29"/>
     </row>
-    <row r="146" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A146" s="97" t="s">
         <v>115</v>
       </c>
@@ -11113,7 +11107,7 @@
         <v>173.309</v>
       </c>
     </row>
-    <row r="147" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A147" s="97" t="s">
         <v>115</v>
       </c>
@@ -11171,7 +11165,7 @@
       </c>
       <c r="AD147" s="21"/>
     </row>
-    <row r="148" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A148" s="97" t="s">
         <v>115</v>
       </c>
@@ -11229,7 +11223,7 @@
       <c r="AB148" s="9"/>
       <c r="AC148" s="9"/>
     </row>
-    <row r="149" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A149" s="97" t="s">
         <v>115</v>
       </c>
@@ -11273,7 +11267,7 @@
       <c r="AB149" s="9"/>
       <c r="AC149" s="9"/>
     </row>
-    <row r="150" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A150" s="97" t="s">
         <v>115</v>
       </c>
@@ -11306,7 +11300,7 @@
       <c r="AB150" s="9"/>
       <c r="AC150" s="9"/>
     </row>
-    <row r="151" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A151" s="97" t="s">
         <v>115</v>
       </c>
@@ -11339,7 +11333,7 @@
       <c r="AB151" s="9"/>
       <c r="AC151" s="9"/>
     </row>
-    <row r="152" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A152" s="97" t="s">
         <v>115</v>
       </c>
@@ -11395,7 +11389,7 @@
       </c>
       <c r="AF152" s="32"/>
     </row>
-    <row r="153" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A153" s="97" t="s">
         <v>115</v>
       </c>
@@ -11450,7 +11444,7 @@
       <c r="AB153" s="9"/>
       <c r="AC153" s="9"/>
     </row>
-    <row r="154" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A154" s="97" t="s">
         <v>115</v>
       </c>
@@ -11505,7 +11499,7 @@
       <c r="AB154" s="9"/>
       <c r="AC154" s="9"/>
     </row>
-    <row r="155" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A155" s="97" t="s">
         <v>115</v>
       </c>
@@ -11550,7 +11544,7 @@
       <c r="AB155" s="9"/>
       <c r="AC155" s="9"/>
     </row>
-    <row r="156" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A156" s="97" t="s">
         <v>115</v>
       </c>
@@ -11620,7 +11614,7 @@
         <v>1.5518181818181764E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A157" s="97" t="s">
         <v>115</v>
       </c>
@@ -11689,7 +11683,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="158" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A158" s="97" t="s">
         <v>115</v>
       </c>
@@ -11762,7 +11756,7 @@
         <v>1.54E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A159" s="97" t="s">
         <v>115</v>
       </c>
@@ -11838,7 +11832,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="160" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A160" s="97" t="s">
         <v>115</v>
       </c>
@@ -11903,7 +11897,7 @@
       <c r="AB160" s="9"/>
       <c r="AC160" s="9"/>
     </row>
-    <row r="161" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A161" s="97" t="s">
         <v>115</v>
       </c>
@@ -11968,7 +11962,7 @@
       <c r="AB161" s="9"/>
       <c r="AC161" s="9"/>
     </row>
-    <row r="162" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A162" s="97" t="s">
         <v>115</v>
       </c>
@@ -12024,7 +12018,7 @@
       </c>
       <c r="AF162" s="32"/>
     </row>
-    <row r="163" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A163" s="97" t="s">
         <v>115</v>
       </c>
@@ -12077,7 +12071,7 @@
       <c r="AB163" s="9"/>
       <c r="AC163" s="9"/>
     </row>
-    <row r="164" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A164" s="97" t="s">
         <v>115</v>
       </c>
@@ -12130,7 +12124,7 @@
       <c r="AB164" s="9"/>
       <c r="AC164" s="9"/>
     </row>
-    <row r="165" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A165" s="97" t="s">
         <v>115</v>
       </c>
@@ -12200,7 +12194,7 @@
         <v>1.7022727272727356E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A166" s="97" t="s">
         <v>115</v>
       </c>
@@ -12269,7 +12263,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="167" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A167" s="97" t="s">
         <v>115</v>
       </c>
@@ -12341,7 +12335,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="168" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A168" s="97" t="s">
         <v>115</v>
       </c>
@@ -12411,7 +12405,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="169" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A169" s="97" t="s">
         <v>115</v>
       </c>
@@ -12483,7 +12477,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="170" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A170" s="97" t="s">
         <v>115</v>
       </c>
@@ -12544,7 +12538,7 @@
       <c r="AC170" s="61"/>
       <c r="AD170" s="29"/>
     </row>
-    <row r="171" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A171" s="97" t="s">
         <v>115</v>
       </c>
@@ -12598,7 +12592,7 @@
       <c r="AC171" s="9"/>
       <c r="AD171" s="29"/>
     </row>
-    <row r="172" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A172" s="97" t="s">
         <v>115</v>
       </c>
@@ -12650,7 +12644,7 @@
       <c r="AC172" s="20"/>
       <c r="AD172" s="91"/>
     </row>
-    <row r="173" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A173" s="97" t="s">
         <v>115</v>
       </c>
@@ -12692,7 +12686,7 @@
       <c r="AC173" s="9"/>
       <c r="AD173" s="29"/>
     </row>
-    <row r="174" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A174" s="97" t="s">
         <v>115</v>
       </c>
@@ -12748,7 +12742,7 @@
       </c>
       <c r="AF174" s="32"/>
     </row>
-    <row r="175" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A175" s="97" t="s">
         <v>115</v>
       </c>
@@ -12813,7 +12807,7 @@
       <c r="AB175" s="9"/>
       <c r="AC175" s="9"/>
     </row>
-    <row r="176" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A176" s="97" t="s">
         <v>115</v>
       </c>
@@ -12878,7 +12872,7 @@
       <c r="AB176" s="9"/>
       <c r="AC176" s="9"/>
     </row>
-    <row r="177" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A177" s="97" t="s">
         <v>115</v>
       </c>
@@ -12943,7 +12937,7 @@
       <c r="AB177" s="9"/>
       <c r="AC177" s="9"/>
     </row>
-    <row r="178" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A178" s="97" t="s">
         <v>115</v>
       </c>
@@ -13008,7 +13002,7 @@
       <c r="AB178" s="9"/>
       <c r="AC178" s="9"/>
     </row>
-    <row r="179" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A179" s="97" t="s">
         <v>115</v>
       </c>
@@ -13068,7 +13062,7 @@
       <c r="AC179" s="20"/>
       <c r="AD179" s="21"/>
     </row>
-    <row r="180" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A180" s="97" t="s">
         <v>115</v>
       </c>
@@ -13128,7 +13122,7 @@
       <c r="AC180" s="20"/>
       <c r="AD180" s="21"/>
     </row>
-    <row r="181" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A181" s="97" t="s">
         <v>115</v>
       </c>
@@ -13198,7 +13192,7 @@
         <v>2.2829545454545408E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A182" s="97" t="s">
         <v>115</v>
       </c>
@@ -13267,7 +13261,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A183" s="97" t="s">
         <v>115</v>
       </c>
@@ -13331,7 +13325,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="184" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A184" s="97" t="s">
         <v>115</v>
       </c>
@@ -13407,7 +13401,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="185" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A185" s="97" t="s">
         <v>115</v>
       </c>
@@ -13479,7 +13473,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="186" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A186" s="97" t="s">
         <v>115</v>
       </c>
@@ -13542,7 +13536,7 @@
       <c r="AC186" s="61"/>
       <c r="AD186" s="29"/>
     </row>
-    <row r="187" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A187" s="97" t="s">
         <v>115</v>
       </c>
@@ -13586,7 +13580,7 @@
       <c r="AC187" s="20"/>
       <c r="AD187" s="91"/>
     </row>
-    <row r="188" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A188" s="97" t="s">
         <v>115</v>
       </c>
@@ -13649,7 +13643,7 @@
       <c r="AC188" s="9"/>
       <c r="AD188" s="29"/>
     </row>
-    <row r="189" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A189" s="97" t="s">
         <v>115</v>
       </c>
@@ -13715,7 +13709,7 @@
       <c r="AB189" s="9"/>
       <c r="AC189" s="9"/>
     </row>
-    <row r="190" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A190" s="97" t="s">
         <v>115</v>
       </c>
@@ -13759,7 +13753,7 @@
       <c r="AC190" s="20"/>
       <c r="AD190" s="91"/>
     </row>
-    <row r="191" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A191" s="97" t="s">
         <v>115</v>
       </c>
@@ -13822,7 +13816,7 @@
       <c r="AC191" s="9"/>
       <c r="AD191" s="29"/>
     </row>
-    <row r="192" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A192" s="97" t="s">
         <v>115</v>
       </c>
@@ -13878,7 +13872,7 @@
       </c>
       <c r="AF192" s="32"/>
     </row>
-    <row r="193" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A193" s="97" t="s">
         <v>115</v>
       </c>
@@ -13943,7 +13937,7 @@
       <c r="AB193" s="9"/>
       <c r="AC193" s="9"/>
     </row>
-    <row r="194" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A194" s="97" t="s">
         <v>115</v>
       </c>
@@ -14008,7 +14002,7 @@
       <c r="AB194" s="9"/>
       <c r="AC194" s="9"/>
     </row>
-    <row r="195" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A195" s="97" t="s">
         <v>115</v>
       </c>
@@ -14061,7 +14055,7 @@
       <c r="AB195" s="9"/>
       <c r="AC195" s="9"/>
     </row>
-    <row r="196" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A196" s="97" t="s">
         <v>115</v>
       </c>
@@ -14118,7 +14112,7 @@
       <c r="AB196" s="9"/>
       <c r="AC196" s="9"/>
     </row>
-    <row r="197" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A197" s="97" t="s">
         <v>115</v>
       </c>
@@ -14162,7 +14156,7 @@
       <c r="AC197" s="20"/>
       <c r="AD197" s="21"/>
     </row>
-    <row r="198" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A198" s="97" t="s">
         <v>115</v>
       </c>
@@ -14206,7 +14200,7 @@
       <c r="AB198" s="9"/>
       <c r="AC198" s="9"/>
     </row>
-    <row r="199" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A199" s="97" t="s">
         <v>115</v>
       </c>
@@ -14276,7 +14270,7 @@
         <v>1.6599999999999948E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A200" s="97" t="s">
         <v>115</v>
       </c>
@@ -14345,7 +14339,7 @@
         <v>2.8199999999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A201" s="97" t="s">
         <v>115</v>
       </c>
@@ -14417,7 +14411,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="202" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A202" s="97" t="s">
         <v>115</v>
       </c>
@@ -14483,7 +14477,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="203" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A203" s="97" t="s">
         <v>115</v>
       </c>
@@ -14557,7 +14551,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="204" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A204" s="97" t="s">
         <v>115</v>
       </c>
@@ -14614,7 +14608,7 @@
       <c r="AC204" s="61"/>
       <c r="AD204" s="29"/>
     </row>
-    <row r="205" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A205" s="97" t="s">
         <v>115</v>
       </c>
@@ -14681,7 +14675,7 @@
       <c r="AC205" s="61"/>
       <c r="AD205" s="29"/>
     </row>
-    <row r="206" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A206" s="97" t="s">
         <v>115</v>
       </c>
@@ -14724,7 +14718,7 @@
       <c r="AC206" s="61"/>
       <c r="AD206" s="29"/>
     </row>
-    <row r="207" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A207" s="97" t="s">
         <v>115</v>
       </c>
@@ -14768,7 +14762,7 @@
       <c r="AC207" s="86"/>
       <c r="AD207" s="91"/>
     </row>
-    <row r="208" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A208" s="97" t="s">
         <v>115</v>
       </c>
@@ -14832,7 +14826,7 @@
       <c r="AC208" s="86"/>
       <c r="AD208" s="91"/>
     </row>
-    <row r="209" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A209" s="97" t="s">
         <v>115</v>
       </c>
@@ -14896,7 +14890,7 @@
       <c r="AB209" s="9"/>
       <c r="AC209" s="9"/>
     </row>
-    <row r="210" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A210" s="97" t="s">
         <v>115</v>
       </c>
@@ -14952,7 +14946,7 @@
       <c r="AB210" s="9"/>
       <c r="AC210" s="9"/>
     </row>
-    <row r="211" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A211" s="97" t="s">
         <v>115</v>
       </c>
@@ -15008,7 +15002,7 @@
       <c r="AB211" s="9"/>
       <c r="AC211" s="9"/>
     </row>
-    <row r="212" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A212" s="97" t="s">
         <v>115</v>
       </c>
@@ -15074,7 +15068,7 @@
       <c r="AC212" s="86"/>
       <c r="AD212" s="91"/>
     </row>
-    <row r="213" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A213" s="97" t="s">
         <v>115</v>
       </c>
@@ -15118,7 +15112,7 @@
       <c r="AC213" s="20"/>
       <c r="AD213" s="21"/>
     </row>
-    <row r="214" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A214" s="97" t="s">
         <v>115</v>
       </c>
@@ -15162,7 +15156,7 @@
       <c r="AB214" s="9"/>
       <c r="AC214" s="9"/>
     </row>
-    <row r="215" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A215" s="97" t="s">
         <v>115</v>
       </c>
@@ -15218,7 +15212,7 @@
       </c>
       <c r="AF215" s="32"/>
     </row>
-    <row r="216" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A216" s="97" t="s">
         <v>115</v>
       </c>
@@ -15285,7 +15279,7 @@
       <c r="AB216" s="9"/>
       <c r="AC216" s="9"/>
     </row>
-    <row r="217" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A217" s="97" t="s">
         <v>115</v>
       </c>
@@ -15352,7 +15346,7 @@
       <c r="AB217" s="9"/>
       <c r="AC217" s="9"/>
     </row>
-    <row r="218" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A218" s="97" t="s">
         <v>115</v>
       </c>
@@ -15419,7 +15413,7 @@
       <c r="AB218" s="9"/>
       <c r="AC218" s="9"/>
     </row>
-    <row r="219" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A219" s="97" t="s">
         <v>115</v>
       </c>
@@ -15486,7 +15480,7 @@
       <c r="AB219" s="9"/>
       <c r="AC219" s="9"/>
     </row>
-    <row r="220" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A220" s="97" t="s">
         <v>115</v>
       </c>
@@ -15530,7 +15524,7 @@
       <c r="AC220" s="20"/>
       <c r="AD220" s="21"/>
     </row>
-    <row r="221" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A221" s="97" t="s">
         <v>115</v>
       </c>
@@ -15574,7 +15568,7 @@
       <c r="AC221" s="20"/>
       <c r="AD221" s="21"/>
     </row>
-    <row r="222" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A222" s="97" t="s">
         <v>115</v>
       </c>
@@ -15646,7 +15640,7 @@
         <v>3.1027739881764438E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A223" s="97" t="s">
         <v>115</v>
       </c>
@@ -15717,7 +15711,7 @@
         <v>2.7699999999999999E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A224" s="97" t="s">
         <v>115</v>
       </c>
@@ -15793,7 +15787,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="225" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A225" s="97" t="s">
         <v>115</v>
       </c>
@@ -15860,7 +15854,7 @@
       <c r="AC225" s="61"/>
       <c r="AD225" s="29"/>
     </row>
-    <row r="226" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A226" s="97" t="s">
         <v>115</v>
       </c>
@@ -15904,7 +15898,7 @@
       <c r="AB226" s="9"/>
       <c r="AC226" s="9"/>
     </row>
-    <row r="227" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A227" s="97" t="s">
         <v>115</v>
       </c>
@@ -15960,7 +15954,7 @@
       </c>
       <c r="AF227" s="32"/>
     </row>
-    <row r="228" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A228" s="97" t="s">
         <v>115</v>
       </c>
@@ -16003,7 +15997,7 @@
       <c r="AB228" s="9"/>
       <c r="AC228" s="9"/>
     </row>
-    <row r="229" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A229" s="97" t="s">
         <v>115</v>
       </c>
@@ -16046,7 +16040,7 @@
       <c r="AB229" s="9"/>
       <c r="AC229" s="9"/>
     </row>
-    <row r="230" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A230" s="97" t="s">
         <v>115</v>
       </c>
@@ -16111,7 +16105,7 @@
       <c r="AB230" s="9"/>
       <c r="AC230" s="9"/>
     </row>
-    <row r="231" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A231" s="97" t="s">
         <v>115</v>
       </c>
@@ -16176,7 +16170,7 @@
       <c r="AB231" s="9"/>
       <c r="AC231" s="9"/>
     </row>
-    <row r="232" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A232" s="97" t="s">
         <v>115</v>
       </c>
@@ -16219,7 +16213,7 @@
       <c r="AB232" s="9"/>
       <c r="AC232" s="9"/>
     </row>
-    <row r="233" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A233" s="97" t="s">
         <v>115</v>
       </c>
@@ -16263,7 +16257,7 @@
       <c r="AB233" s="9"/>
       <c r="AC233" s="9"/>
     </row>
-    <row r="234" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A234" s="97" t="s">
         <v>115</v>
       </c>
@@ -16335,7 +16329,7 @@
         <v>3.3560606060606069E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A235" s="97" t="s">
         <v>115</v>
       </c>
@@ -16408,7 +16402,7 @@
         <v>3.6499999999999998E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A236" s="97" t="s">
         <v>115</v>
       </c>
@@ -16474,7 +16468,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="237" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A237" s="97" t="s">
         <v>115</v>
       </c>
@@ -16552,7 +16546,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="238" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A238" s="97" t="s">
         <v>115</v>
       </c>
@@ -16616,7 +16610,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="239" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A239" s="97" t="s">
         <v>115</v>
       </c>
@@ -16674,7 +16668,7 @@
       <c r="AC239" s="61"/>
       <c r="AD239" s="29"/>
     </row>
-    <row r="240" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A240" s="97" t="s">
         <v>115</v>
       </c>
@@ -16743,7 +16737,7 @@
       <c r="AC240" s="61"/>
       <c r="AD240" s="29"/>
     </row>
-    <row r="241" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A241" s="97" t="s">
         <v>115</v>
       </c>
@@ -16798,7 +16792,7 @@
       <c r="AC241" s="61"/>
       <c r="AD241" s="29"/>
     </row>
-    <row r="242" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A242" s="97" t="s">
         <v>115</v>
       </c>
@@ -16860,7 +16854,7 @@
       <c r="AC242" s="86"/>
       <c r="AD242" s="91"/>
     </row>
-    <row r="243" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A243" s="97" t="s">
         <v>115</v>
       </c>
@@ -16904,7 +16898,7 @@
       <c r="AB243" s="9"/>
       <c r="AC243" s="9"/>
     </row>
-    <row r="244" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A244" s="97" t="s">
         <v>115</v>
       </c>
@@ -16960,7 +16954,7 @@
       </c>
       <c r="AF244" s="32"/>
     </row>
-    <row r="245" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A245" s="97" t="s">
         <v>115</v>
       </c>
@@ -17003,7 +16997,7 @@
       <c r="AB245" s="9"/>
       <c r="AC245" s="9"/>
     </row>
-    <row r="246" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A246" s="97" t="s">
         <v>115</v>
       </c>
@@ -17057,7 +17051,7 @@
       <c r="AB246" s="9"/>
       <c r="AC246" s="9"/>
     </row>
-    <row r="247" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A247" s="97" t="s">
         <v>115</v>
       </c>
@@ -17122,7 +17116,7 @@
       <c r="AB247" s="9"/>
       <c r="AC247" s="9"/>
     </row>
-    <row r="248" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A248" s="97" t="s">
         <v>115</v>
       </c>
@@ -17187,7 +17181,7 @@
       <c r="AB248" s="9"/>
       <c r="AC248" s="9"/>
     </row>
-    <row r="249" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A249" s="97" t="s">
         <v>115</v>
       </c>
@@ -17241,7 +17235,7 @@
       <c r="AC249" s="20"/>
       <c r="AD249" s="21"/>
     </row>
-    <row r="250" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A250" s="97" t="s">
         <v>115</v>
       </c>
@@ -17295,7 +17289,7 @@
       <c r="AC250" s="20"/>
       <c r="AD250" s="21"/>
     </row>
-    <row r="251" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A251" s="97" t="s">
         <v>115</v>
       </c>
@@ -17369,7 +17363,7 @@
         <v>3.8397727272727278E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A252" s="97" t="s">
         <v>115</v>
       </c>
@@ -17442,7 +17436,7 @@
         <v>6.3500000000000001E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A253" s="97" t="s">
         <v>115</v>
       </c>
@@ -17507,7 +17501,7 @@
       <c r="AC253" s="62"/>
       <c r="AD253" s="126"/>
     </row>
-    <row r="254" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A254" s="97" t="s">
         <v>115</v>
       </c>
@@ -17581,7 +17575,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="255" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A255" s="97" t="s">
         <v>115</v>
       </c>
@@ -17633,7 +17627,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="256" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A256" s="97" t="s">
         <v>115</v>
       </c>
@@ -17711,7 +17705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="257" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A257" s="97" t="s">
         <v>115</v>
       </c>
@@ -17755,7 +17749,7 @@
       <c r="AC257" s="86"/>
       <c r="AD257" s="91"/>
     </row>
-    <row r="258" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A258" s="97" t="s">
         <v>115</v>
       </c>
@@ -17812,7 +17806,7 @@
       <c r="AC258" s="9"/>
       <c r="AD258" s="29"/>
     </row>
-    <row r="259" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A259" s="97" t="s">
         <v>115</v>
       </c>
@@ -17880,7 +17874,7 @@
       <c r="AB259" s="9"/>
       <c r="AC259" s="9"/>
     </row>
-    <row r="260" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A260" s="97" t="s">
         <v>115</v>
       </c>
@@ -17921,7 +17915,7 @@
       <c r="AC260" s="86"/>
       <c r="AD260" s="91"/>
     </row>
-    <row r="261" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A261" s="97" t="s">
         <v>115</v>
       </c>
@@ -17976,7 +17970,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="262" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A262" s="97" t="s">
         <v>115</v>
       </c>
@@ -18020,7 +18014,7 @@
       <c r="AB262" s="9"/>
       <c r="AC262" s="9"/>
     </row>
-    <row r="263" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A263" s="97" t="s">
         <v>115</v>
       </c>
@@ -18082,7 +18076,7 @@
       <c r="AB263" s="9"/>
       <c r="AC263" s="9"/>
     </row>
-    <row r="264" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A264" s="97" t="s">
         <v>115</v>
       </c>
@@ -18147,7 +18141,7 @@
       <c r="AB264" s="9"/>
       <c r="AC264" s="9"/>
     </row>
-    <row r="265" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A265" s="97" t="s">
         <v>115</v>
       </c>
@@ -18212,7 +18206,7 @@
       <c r="AB265" s="9"/>
       <c r="AC265" s="9"/>
     </row>
-    <row r="266" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A266" s="97" t="s">
         <v>115</v>
       </c>
@@ -18253,7 +18247,7 @@
       <c r="AC266" s="20"/>
       <c r="AD266" s="21"/>
     </row>
-    <row r="267" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A267" s="97" t="s">
         <v>115</v>
       </c>
@@ -18327,7 +18321,7 @@
         <v>5.2856060606060629E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A268" s="97" t="s">
         <v>115</v>
       </c>
@@ -18400,7 +18394,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A269" s="97" t="s">
         <v>115</v>
       </c>
@@ -18478,7 +18472,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="270" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A270" s="97" t="s">
         <v>115</v>
       </c>
@@ -18558,7 +18552,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="271" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A271" s="97" t="s">
         <v>115</v>
       </c>
@@ -18612,7 +18606,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="272" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A272" s="97" t="s">
         <v>115</v>
       </c>
@@ -18657,7 +18651,7 @@
       <c r="AC272" s="61"/>
       <c r="AD272" s="126"/>
     </row>
-    <row r="273" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A273" s="97" t="s">
         <v>115</v>
       </c>
@@ -18712,7 +18706,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="274" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A274" s="97" t="s">
         <v>115</v>
       </c>
@@ -18769,7 +18763,7 @@
       <c r="AC274" s="9"/>
       <c r="AD274" s="29"/>
     </row>
-    <row r="275" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A275" s="97" t="s">
         <v>115</v>
       </c>
@@ -18831,7 +18825,7 @@
       <c r="AB275" s="9"/>
       <c r="AC275" s="9"/>
     </row>
-    <row r="276" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A276" s="97" t="s">
         <v>115</v>
       </c>
@@ -18894,7 +18888,7 @@
       <c r="AC276" s="61"/>
       <c r="AD276" s="29"/>
     </row>
-    <row r="277" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A277" s="97" t="s">
         <v>115</v>
       </c>
@@ -18954,7 +18948,7 @@
       <c r="AC277" s="21"/>
       <c r="AD277" s="21"/>
     </row>
-    <row r="278" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A278" s="97" t="s">
         <v>115</v>
       </c>
@@ -18999,7 +18993,7 @@
       <c r="AB278" s="9"/>
       <c r="AC278" s="9"/>
     </row>
-    <row r="279" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A279" s="97" t="s">
         <v>115</v>
       </c>
@@ -19073,7 +19067,7 @@
         <v>3.8438095238095271E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A280" s="97" t="s">
         <v>115</v>
       </c>
@@ -19146,7 +19140,7 @@
         <v>3.85E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A281" s="97" t="s">
         <v>115</v>
       </c>
@@ -19224,7 +19218,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="282" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A282" s="97" t="s">
         <v>115</v>
       </c>
@@ -19302,7 +19296,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A283" s="97" t="s">
         <v>115</v>
       </c>
@@ -19377,7 +19371,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="284" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A284" s="97" t="s">
         <v>115</v>
       </c>
@@ -19445,7 +19439,7 @@
       <c r="AB284" s="9"/>
       <c r="AC284" s="9"/>
     </row>
-    <row r="285" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A285" s="97" t="s">
         <v>115</v>
       </c>
@@ -19510,7 +19504,7 @@
       <c r="AC285" s="61"/>
       <c r="AD285" s="29"/>
     </row>
-    <row r="286" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A286" s="97" t="s">
         <v>115</v>
       </c>
@@ -19572,7 +19566,7 @@
       <c r="AC286" s="86"/>
       <c r="AD286" s="91"/>
     </row>
-    <row r="287" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A287" s="97" t="s">
         <v>115</v>
       </c>
@@ -19640,7 +19634,7 @@
       <c r="AB287" s="9"/>
       <c r="AC287" s="9"/>
     </row>
-    <row r="288" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A288" s="97" t="s">
         <v>115</v>
       </c>
@@ -19685,7 +19679,7 @@
       <c r="S288" s="60"/>
       <c r="V288" s="146"/>
     </row>
-    <row r="289" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A289" s="97" t="s">
         <v>115</v>
       </c>
@@ -19737,7 +19731,7 @@
       <c r="AC289" s="86"/>
       <c r="AD289" s="91"/>
     </row>
-    <row r="290" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A290" s="97" t="s">
         <v>115</v>
       </c>
@@ -19793,7 +19787,7 @@
       </c>
       <c r="AF290" s="32"/>
     </row>
-    <row r="291" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A291" s="97" t="s">
         <v>115</v>
       </c>
@@ -19858,7 +19852,7 @@
       <c r="AB291" s="9"/>
       <c r="AC291" s="9"/>
     </row>
-    <row r="292" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A292" s="97" t="s">
         <v>115</v>
       </c>
@@ -19923,7 +19917,7 @@
       <c r="AB292" s="9"/>
       <c r="AC292" s="9"/>
     </row>
-    <row r="293" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A293" s="97" t="s">
         <v>115</v>
       </c>
@@ -19985,7 +19979,7 @@
       <c r="AB293" s="9"/>
       <c r="AC293" s="9"/>
     </row>
-    <row r="294" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A294" s="97" t="s">
         <v>115</v>
       </c>
@@ -20045,7 +20039,7 @@
       <c r="AC294" s="20"/>
       <c r="AD294" s="21"/>
     </row>
-    <row r="295" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A295" s="97" t="s">
         <v>115</v>
       </c>
@@ -20089,7 +20083,7 @@
       <c r="AB295" s="9"/>
       <c r="AC295" s="9"/>
     </row>
-    <row r="296" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A296" s="97" t="s">
         <v>115</v>
       </c>
@@ -20163,7 +20157,7 @@
         <v>4.2545959595959637E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A297" s="97" t="s">
         <v>115</v>
       </c>
@@ -20236,7 +20230,7 @@
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A298" s="97" t="s">
         <v>115</v>
       </c>
@@ -20314,7 +20308,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="299" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A299" s="97" t="s">
         <v>115</v>
       </c>
@@ -20392,7 +20386,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="300" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A300" s="97" t="s">
         <v>115</v>
       </c>
@@ -20466,7 +20460,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="301" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A301" s="97" t="s">
         <v>115</v>
       </c>
@@ -20526,7 +20520,7 @@
       <c r="AC301" s="20"/>
       <c r="AD301" s="21"/>
     </row>
-    <row r="302" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A302" s="97" t="s">
         <v>115</v>
       </c>
@@ -20597,7 +20591,7 @@
       <c r="AC302" s="9"/>
       <c r="AD302" s="29"/>
     </row>
-    <row r="303" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A303" s="97" t="s">
         <v>115</v>
       </c>
@@ -20660,7 +20654,7 @@
       <c r="AC303" s="9"/>
       <c r="AD303" s="29"/>
     </row>
-    <row r="304" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A304" s="97" t="s">
         <v>115</v>
       </c>
@@ -20720,7 +20714,7 @@
       <c r="AC304" s="20"/>
       <c r="AD304" s="21"/>
     </row>
-    <row r="305" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A305" s="97" t="s">
         <v>115</v>
       </c>
@@ -20764,7 +20758,7 @@
       <c r="AB305" s="9"/>
       <c r="AC305" s="9"/>
     </row>
-    <row r="306" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A306" s="97" t="s">
         <v>115</v>
       </c>
@@ -20820,7 +20814,7 @@
       </c>
       <c r="AF306" s="32"/>
     </row>
-    <row r="307" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A307" s="97" t="s">
         <v>115</v>
       </c>
@@ -20882,7 +20876,7 @@
       <c r="AB307" s="9"/>
       <c r="AC307" s="9"/>
     </row>
-    <row r="308" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A308" s="97" t="s">
         <v>115</v>
       </c>
@@ -20947,7 +20941,7 @@
       <c r="AB308" s="9"/>
       <c r="AC308" s="9"/>
     </row>
-    <row r="309" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A309" s="97" t="s">
         <v>115</v>
       </c>
@@ -21012,7 +21006,7 @@
       <c r="AB309" s="9"/>
       <c r="AC309" s="9"/>
     </row>
-    <row r="310" spans="1:32" ht="15.75" hidden="1" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:32" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A310" s="97" t="s">
         <v>115</v>
       </c>
@@ -21072,7 +21066,7 @@
       <c r="AC310" s="20"/>
       <c r="AD310" s="21"/>
     </row>
-    <row r="311" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A311" s="97" t="s">
         <v>115</v>
       </c>
@@ -21146,7 +21140,7 @@
         <v>3.8193181818181654E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A312" s="97" t="s">
         <v>115</v>
       </c>
@@ -21219,7 +21213,7 @@
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A313" s="97" t="s">
         <v>115</v>
       </c>
@@ -21297,7 +21291,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="314" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A314" s="97" t="s">
         <v>115</v>
       </c>
@@ -21375,7 +21369,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="315" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A315" s="97" t="s">
         <v>115</v>
       </c>
@@ -21449,7 +21443,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="316" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A316" s="97" t="s">
         <v>115</v>
       </c>
@@ -21509,7 +21503,7 @@
       <c r="AC316" s="86"/>
       <c r="AD316" s="154"/>
     </row>
-    <row r="317" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A317" s="97" t="s">
         <v>115</v>
       </c>
@@ -21580,7 +21574,7 @@
       <c r="AC317" s="9"/>
       <c r="AD317" s="29"/>
     </row>
-    <row r="318" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A318" s="97" t="s">
         <v>115</v>
       </c>
@@ -21643,7 +21637,7 @@
       <c r="AC318" s="9"/>
       <c r="AD318" s="29"/>
     </row>
-    <row r="319" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A319" s="97" t="s">
         <v>115</v>
       </c>
@@ -21703,7 +21697,7 @@
       <c r="AC319" s="20"/>
       <c r="AD319" s="21"/>
     </row>
-    <row r="320" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A320" s="97" t="s">
         <v>115</v>
       </c>
@@ -21747,7 +21741,7 @@
       <c r="AB320" s="9"/>
       <c r="AC320" s="9"/>
     </row>
-    <row r="321" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A321" s="97" t="s">
         <v>115</v>
       </c>
@@ -21803,7 +21797,7 @@
       </c>
       <c r="AF321" s="32"/>
     </row>
-    <row r="322" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A322" s="97" t="s">
         <v>115</v>
       </c>
@@ -21865,7 +21859,7 @@
       <c r="AB322" s="9"/>
       <c r="AC322" s="9"/>
     </row>
-    <row r="323" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A323" s="97" t="s">
         <v>115</v>
       </c>
@@ -21930,7 +21924,7 @@
       <c r="AB323" s="9"/>
       <c r="AC323" s="9"/>
     </row>
-    <row r="324" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A324" s="97" t="s">
         <v>115</v>
       </c>
@@ -21995,7 +21989,7 @@
       <c r="AB324" s="9"/>
       <c r="AC324" s="9"/>
     </row>
-    <row r="325" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A325" s="97" t="s">
         <v>115</v>
       </c>
@@ -22055,7 +22049,7 @@
       <c r="AC325" s="20"/>
       <c r="AD325" s="21"/>
     </row>
-    <row r="326" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A326" s="97" t="s">
         <v>115</v>
       </c>
@@ -22129,7 +22123,7 @@
         <v>3.8136363636363524E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A327" s="97" t="s">
         <v>115</v>
       </c>
@@ -22202,7 +22196,7 @@
         <v>2.6200000000000001E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A328" s="97" t="s">
         <v>115</v>
       </c>
@@ -22266,7 +22260,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="329" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A329" s="97" t="s">
         <v>115</v>
       </c>
@@ -22340,7 +22334,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="330" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A330" s="97" t="s">
         <v>115</v>
       </c>
@@ -22418,7 +22412,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="331" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A331" s="97" t="s">
         <v>115</v>
       </c>
@@ -22480,7 +22474,7 @@
       <c r="AC331" s="86"/>
       <c r="AD331" s="91"/>
     </row>
-    <row r="332" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A332" s="97" t="s">
         <v>115</v>
       </c>
@@ -22543,7 +22537,7 @@
       <c r="AC332" s="9"/>
       <c r="AD332" s="29"/>
     </row>
-    <row r="333" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A333" s="97" t="s">
         <v>115</v>
       </c>
@@ -22615,7 +22609,7 @@
       <c r="AC333" s="9"/>
       <c r="AD333" s="29"/>
     </row>
-    <row r="334" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A334" s="97" t="s">
         <v>115</v>
       </c>
@@ -22675,7 +22669,7 @@
       <c r="AC334" s="20"/>
       <c r="AD334" s="91"/>
     </row>
-    <row r="335" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A335" s="97" t="s">
         <v>115</v>
       </c>
@@ -22731,7 +22725,7 @@
       </c>
       <c r="AF335" s="32"/>
     </row>
-    <row r="336" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A336" s="97" t="s">
         <v>115</v>
       </c>
@@ -22775,7 +22769,7 @@
       <c r="AB336" s="9"/>
       <c r="AC336" s="9"/>
     </row>
-    <row r="337" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A337" s="97" t="s">
         <v>115</v>
       </c>
@@ -22837,7 +22831,7 @@
       <c r="AB337" s="9"/>
       <c r="AC337" s="9"/>
     </row>
-    <row r="338" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A338" s="97" t="s">
         <v>115</v>
       </c>
@@ -22902,7 +22896,7 @@
       <c r="AB338" s="9"/>
       <c r="AC338" s="9"/>
     </row>
-    <row r="339" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A339" s="97" t="s">
         <v>115</v>
       </c>
@@ -22967,7 +22961,7 @@
       <c r="AB339" s="9"/>
       <c r="AC339" s="9"/>
     </row>
-    <row r="340" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A340" s="97" t="s">
         <v>115</v>
       </c>
@@ -23011,7 +23005,7 @@
       <c r="AC340" s="20"/>
       <c r="AD340" s="21"/>
     </row>
-    <row r="341" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A341" s="97" t="s">
         <v>115</v>
       </c>
@@ -23056,7 +23050,7 @@
       <c r="AB341" s="9"/>
       <c r="AC341" s="9"/>
     </row>
-    <row r="342" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A342" s="162" t="s">
         <v>115</v>
       </c>
@@ -24430,7 +24424,7 @@
         <v>3.2386363636363602E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A364" s="97" t="s">
         <v>115</v>
       </c>
@@ -24503,7 +24497,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A365" s="97" t="s">
         <v>115</v>
       </c>
@@ -24570,7 +24564,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="366" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A366" s="97" t="s">
         <v>115</v>
       </c>
@@ -24637,7 +24631,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="367" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A367" s="97" t="s">
         <v>115</v>
       </c>
@@ -24687,7 +24681,7 @@
         <v>5.0017045454545439E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:31" hidden="1" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A368" s="97" t="s">
         <v>115</v>
       </c>
@@ -24754,7 +24748,7 @@
       <c r="AC368" s="61"/>
       <c r="AD368" s="29"/>
     </row>
-    <row r="369" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A369" s="97" t="s">
         <v>115</v>
       </c>
@@ -24816,7 +24810,7 @@
       <c r="AC369" s="61"/>
       <c r="AD369" s="29"/>
     </row>
-    <row r="370" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A370" s="97" t="s">
         <v>115</v>
       </c>
@@ -24876,7 +24870,7 @@
       <c r="AC370" s="9"/>
       <c r="AD370" s="29"/>
     </row>
-    <row r="371" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A371" s="97" t="s">
         <v>115</v>
       </c>
@@ -24918,7 +24912,7 @@
       <c r="AC371" s="9"/>
       <c r="AD371" s="29"/>
     </row>
-    <row r="372" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A372" s="97" t="s">
         <v>115</v>
       </c>
@@ -24974,7 +24968,7 @@
       </c>
       <c r="AF372" s="32"/>
     </row>
-    <row r="373" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A373" s="97" t="s">
         <v>115</v>
       </c>
@@ -25018,7 +25012,7 @@
       <c r="AB373" s="9"/>
       <c r="AC373" s="9"/>
     </row>
-    <row r="374" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A374" s="97" t="s">
         <v>115</v>
       </c>
@@ -25080,7 +25074,7 @@
       <c r="AB374" s="9"/>
       <c r="AC374" s="9"/>
     </row>
-    <row r="375" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A375" s="97" t="s">
         <v>115</v>
       </c>
@@ -25145,7 +25139,7 @@
       <c r="AB375" s="9"/>
       <c r="AC375" s="9"/>
     </row>
-    <row r="376" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A376" s="97" t="s">
         <v>115</v>
       </c>
@@ -25203,7 +25197,7 @@
       <c r="AC376" s="20"/>
       <c r="AD376" s="21"/>
     </row>
-    <row r="377" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A377" s="97" t="s">
         <v>115</v>
       </c>
@@ -25246,7 +25240,7 @@
       <c r="AB377" s="9"/>
       <c r="AC377" s="9"/>
     </row>
-    <row r="378" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A378" s="97" t="s">
         <v>115</v>
       </c>
@@ -25320,7 +25314,7 @@
         <v>5.0017045454545439E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A379" s="97" t="s">
         <v>115</v>
       </c>
@@ -25393,7 +25387,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="380" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A380" s="97" t="s">
         <v>115</v>
       </c>
@@ -25471,7 +25465,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="381" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A381" s="97" t="s">
         <v>115</v>
       </c>
@@ -25545,7 +25539,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="382" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A382" s="97" t="s">
         <v>115</v>
       </c>
@@ -25595,7 +25589,7 @@
         <v>5.7299999999999962E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A383" s="97" t="s">
         <v>115</v>
       </c>
@@ -25666,7 +25660,7 @@
       <c r="AC383" s="61"/>
       <c r="AD383" s="29"/>
     </row>
-    <row r="384" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A384" s="97" t="s">
         <v>115</v>
       </c>
@@ -25729,7 +25723,7 @@
       <c r="AC384" s="9"/>
       <c r="AD384" s="29"/>
     </row>
-    <row r="385" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A385" s="97" t="s">
         <v>115</v>
       </c>
@@ -25773,7 +25767,7 @@
       <c r="AC385" s="9"/>
       <c r="AD385" s="29"/>
     </row>
-    <row r="386" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A386" s="97" t="s">
         <v>115</v>
       </c>
@@ -25829,7 +25823,7 @@
       </c>
       <c r="AF386" s="32"/>
     </row>
-    <row r="387" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A387" s="97" t="s">
         <v>115</v>
       </c>
@@ -25873,7 +25867,7 @@
       <c r="AB387" s="9"/>
       <c r="AC387" s="9"/>
     </row>
-    <row r="388" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A388" s="97" t="s">
         <v>115</v>
       </c>
@@ -25935,7 +25929,7 @@
       <c r="AB388" s="9"/>
       <c r="AC388" s="9"/>
     </row>
-    <row r="389" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A389" s="97" t="s">
         <v>115</v>
       </c>
@@ -25983,7 +25977,7 @@
       <c r="AB389" s="9"/>
       <c r="AC389" s="9"/>
     </row>
-    <row r="390" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A390" s="97" t="s">
         <v>115</v>
       </c>
@@ -26045,7 +26039,7 @@
       <c r="AB390" s="9"/>
       <c r="AC390" s="9"/>
     </row>
-    <row r="391" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A391" s="97" t="s">
         <v>115</v>
       </c>
@@ -26089,7 +26083,7 @@
       <c r="AC391" s="20"/>
       <c r="AD391" s="21"/>
     </row>
-    <row r="392" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A392" s="97" t="s">
         <v>115</v>
       </c>
@@ -26163,7 +26157,7 @@
         <v>5.7300000000000018E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A393" s="97" t="s">
         <v>115</v>
       </c>
@@ -26236,7 +26230,7 @@
         <v>6.54E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A394" s="97" t="s">
         <v>115</v>
       </c>
@@ -26309,7 +26303,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="395" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A395" s="97" t="s">
         <v>115</v>
       </c>
@@ -26373,7 +26367,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="396" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A396" s="97" t="s">
         <v>115</v>
       </c>
@@ -26444,7 +26438,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="397" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A397" s="97" t="s">
         <v>115</v>
       </c>
@@ -26520,7 +26514,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="398" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A398" s="97" t="s">
         <v>115</v>
       </c>
@@ -26575,7 +26569,7 @@
       <c r="AC398" s="61"/>
       <c r="AD398" s="29"/>
     </row>
-    <row r="399" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A399" s="97" t="s">
         <v>115</v>
       </c>
@@ -26637,7 +26631,7 @@
       <c r="AC399" s="61"/>
       <c r="AD399" s="29"/>
     </row>
-    <row r="400" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A400" s="97" t="s">
         <v>115</v>
       </c>
@@ -26699,7 +26693,7 @@
       <c r="AC400" s="9"/>
       <c r="AD400" s="29"/>
     </row>
-    <row r="401" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A401" s="97" t="s">
         <v>115</v>
       </c>
@@ -26743,7 +26737,7 @@
       <c r="AC401" s="9"/>
       <c r="AD401" s="29"/>
     </row>
-    <row r="402" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A402" s="97" t="s">
         <v>115</v>
       </c>
@@ -26799,7 +26793,7 @@
       </c>
       <c r="AF402" s="32"/>
     </row>
-    <row r="403" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A403" s="97" t="s">
         <v>115</v>
       </c>
@@ -26843,7 +26837,7 @@
       <c r="AB403" s="9"/>
       <c r="AC403" s="9"/>
     </row>
-    <row r="404" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A404" s="97" t="s">
         <v>115</v>
       </c>
@@ -26905,7 +26899,7 @@
       <c r="AB404" s="9"/>
       <c r="AC404" s="9"/>
     </row>
-    <row r="405" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A405" s="97" t="s">
         <v>115</v>
       </c>
@@ -26968,7 +26962,7 @@
       <c r="AB405" s="9"/>
       <c r="AC405" s="9"/>
     </row>
-    <row r="406" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A406" s="97" t="s">
         <v>115</v>
       </c>
@@ -27025,7 +27019,7 @@
       <c r="AB406" s="9"/>
       <c r="AC406" s="9"/>
     </row>
-    <row r="407" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A407" s="97" t="s">
         <v>115</v>
       </c>
@@ -27068,7 +27062,7 @@
       <c r="AB407" s="9"/>
       <c r="AC407" s="9"/>
     </row>
-    <row r="408" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A408" s="184" t="s">
         <v>115</v>
       </c>
@@ -27142,7 +27136,7 @@
         <v>3.7732954545454445E-2</v>
       </c>
     </row>
-    <row r="409" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A409" s="97" t="s">
         <v>115</v>
       </c>
@@ -27215,7 +27209,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="410" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A410" s="97" t="s">
         <v>115</v>
       </c>
@@ -27288,7 +27282,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="411" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A411" s="97" t="s">
         <v>115</v>
       </c>
@@ -27352,7 +27346,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="412" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A412" s="97" t="s">
         <v>115</v>
       </c>
@@ -27423,7 +27417,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="413" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A413" s="97" t="s">
         <v>115</v>
       </c>
@@ -27499,7 +27493,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="414" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A414" s="97" t="s">
         <v>115</v>
       </c>
@@ -27554,7 +27548,7 @@
       <c r="AC414" s="61"/>
       <c r="AD414" s="29"/>
     </row>
-    <row r="415" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A415" s="97" t="s">
         <v>115</v>
       </c>
@@ -27616,7 +27610,7 @@
       <c r="AC415" s="61"/>
       <c r="AD415" s="29"/>
     </row>
-    <row r="416" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A416" s="97" t="s">
         <v>115</v>
       </c>
@@ -27678,7 +27672,7 @@
       <c r="AC416" s="9"/>
       <c r="AD416" s="29"/>
     </row>
-    <row r="417" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A417" s="97" t="s">
         <v>115</v>
       </c>
@@ -27722,7 +27716,7 @@
       <c r="AC417" s="9"/>
       <c r="AD417" s="29"/>
     </row>
-    <row r="418" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A418" s="97" t="s">
         <v>115</v>
       </c>
@@ -27774,7 +27768,7 @@
       </c>
       <c r="AF418" s="32"/>
     </row>
-    <row r="419" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A419" s="97" t="s">
         <v>115</v>
       </c>
@@ -27818,7 +27812,7 @@
       <c r="AB419" s="9"/>
       <c r="AC419" s="9"/>
     </row>
-    <row r="420" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A420" s="97" t="s">
         <v>115</v>
       </c>
@@ -27880,7 +27874,7 @@
       <c r="AB420" s="9"/>
       <c r="AC420" s="9"/>
     </row>
-    <row r="421" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A421" s="97" t="s">
         <v>115</v>
       </c>
@@ -27943,7 +27937,7 @@
       <c r="AB421" s="9"/>
       <c r="AC421" s="9"/>
     </row>
-    <row r="422" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A422" s="97" t="s">
         <v>115</v>
       </c>
@@ -28000,7 +27994,7 @@
       <c r="AB422" s="9"/>
       <c r="AC422" s="9"/>
     </row>
-    <row r="423" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A423" s="97" t="s">
         <v>115</v>
       </c>
@@ -28043,7 +28037,7 @@
       <c r="AB423" s="9"/>
       <c r="AC423" s="9"/>
     </row>
-    <row r="424" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A424" s="97" t="s">
         <v>115</v>
       </c>
@@ -28117,7 +28111,7 @@
         <v>3.7732954545454556E-2</v>
       </c>
     </row>
-    <row r="425" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A425" s="97" t="s">
         <v>115</v>
       </c>
@@ -28190,7 +28184,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="426" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A426" s="97" t="s">
         <v>115</v>
       </c>
@@ -28263,7 +28257,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="427" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A427" s="97" t="s">
         <v>115</v>
       </c>
@@ -28330,7 +28324,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="428" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A428" s="97"/>
       <c r="B428" s="49"/>
       <c r="C428" s="5"/>
@@ -28370,7 +28364,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="429" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A429" s="97" t="s">
         <v>115</v>
       </c>
@@ -28436,7 +28430,7 @@
       <c r="AB429" s="18"/>
       <c r="AD429" s="19"/>
     </row>
-    <row r="430" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A430" s="97" t="s">
         <v>115</v>
       </c>
@@ -28483,7 +28477,7 @@
       <c r="AB430" s="18"/>
       <c r="AD430" s="19"/>
     </row>
-    <row r="431" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A431" s="97"/>
       <c r="B431" s="49"/>
       <c r="C431" s="5"/>
@@ -28512,7 +28506,7 @@
       <c r="AB431" s="18"/>
       <c r="AD431" s="19"/>
     </row>
-    <row r="432" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A432" s="97" t="s">
         <v>115</v>
       </c>
@@ -28541,7 +28535,7 @@
       <c r="AB432" s="18"/>
       <c r="AD432" s="19"/>
     </row>
-    <row r="433" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A433" s="97" t="s">
         <v>115</v>
       </c>
@@ -28585,7 +28579,7 @@
       <c r="AC433" s="9"/>
       <c r="AD433" s="29"/>
     </row>
-    <row r="434" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A434" s="97" t="s">
         <v>115</v>
       </c>
@@ -28637,7 +28631,7 @@
       </c>
       <c r="AF434" s="32"/>
     </row>
-    <row r="435" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A435" s="97" t="s">
         <v>115</v>
       </c>
@@ -28681,7 +28675,7 @@
       <c r="AB435" s="9"/>
       <c r="AC435" s="9"/>
     </row>
-    <row r="436" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A436" s="97" t="s">
         <v>115</v>
       </c>
@@ -28706,15 +28700,30 @@
       <c r="H436" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J436" s="38">
-        <v>46132</v>
-      </c>
-      <c r="L436" s="26"/>
-      <c r="M436" s="18"/>
-      <c r="N436" s="18"/>
-      <c r="O436" s="18"/>
-      <c r="P436" s="27"/>
-      <c r="Q436" s="18"/>
+      <c r="I436" t="s">
+        <v>304</v>
+      </c>
+      <c r="J436" s="11">
+        <v>46128</v>
+      </c>
+      <c r="L436" s="26">
+        <v>3722</v>
+      </c>
+      <c r="M436" s="18">
+        <v>11.62</v>
+      </c>
+      <c r="N436" s="18">
+        <v>0.68</v>
+      </c>
+      <c r="O436" s="18">
+        <v>0.91</v>
+      </c>
+      <c r="P436" s="27">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q436" s="18">
+        <v>0.75</v>
+      </c>
       <c r="R436" s="18"/>
       <c r="S436" s="18"/>
       <c r="T436" s="26"/>
@@ -28728,7 +28737,7 @@
       <c r="AB436" s="9"/>
       <c r="AC436" s="9"/>
     </row>
-    <row r="437" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A437" s="97" t="s">
         <v>115</v>
       </c>
@@ -28772,7 +28781,7 @@
       <c r="AB437" s="9"/>
       <c r="AC437" s="9"/>
     </row>
-    <row r="438" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A438" s="97" t="s">
         <v>115</v>
       </c>
@@ -28806,7 +28815,7 @@
       <c r="AB438" s="18"/>
       <c r="AD438" s="19"/>
     </row>
-    <row r="439" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A439" s="97" t="s">
         <v>115</v>
       </c>
@@ -28835,7 +28844,7 @@
       <c r="AB439" s="18"/>
       <c r="AD439" s="19"/>
     </row>
-    <row r="440" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A440" s="97" t="s">
         <v>115</v>
       </c>
@@ -28909,7 +28918,7 @@
         <v>3.8238095238095293E-2</v>
       </c>
     </row>
-    <row r="441" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A441" s="97" t="s">
         <v>115</v>
       </c>
@@ -28982,7 +28991,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="442" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A442" s="97" t="s">
         <v>115</v>
       </c>
@@ -29011,7 +29020,7 @@
       <c r="AB442" s="18"/>
       <c r="AD442" s="19"/>
     </row>
-    <row r="443" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A443" s="97" t="s">
         <v>115</v>
       </c>
@@ -29040,7 +29049,7 @@
       <c r="AB443" s="18"/>
       <c r="AD443" s="19"/>
     </row>
-    <row r="444" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A444" s="97"/>
       <c r="B444" s="49"/>
       <c r="C444" s="5"/>
@@ -29054,7 +29063,7 @@
       <c r="AB444" s="18"/>
       <c r="AD444" s="19"/>
     </row>
-    <row r="445" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A445" s="97" t="s">
         <v>115</v>
       </c>
@@ -29083,7 +29092,7 @@
       <c r="AB445" s="18"/>
       <c r="AD445" s="19"/>
     </row>
-    <row r="446" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A446" s="97" t="s">
         <v>115</v>
       </c>
@@ -29112,7 +29121,7 @@
       <c r="AB446" s="18"/>
       <c r="AD446" s="19"/>
     </row>
-    <row r="447" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A447" s="97" t="s">
         <v>115</v>
       </c>
@@ -29141,7 +29150,7 @@
       <c r="AB447" s="18"/>
       <c r="AD447" s="19"/>
     </row>
-    <row r="448" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A448" s="97" t="s">
         <v>115</v>
       </c>
@@ -29170,7 +29179,7 @@
       <c r="AB448" s="18"/>
       <c r="AD448" s="19"/>
     </row>
-    <row r="449" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A449" s="97" t="s">
         <v>115</v>
       </c>
@@ -29214,7 +29223,7 @@
       <c r="AC449" s="9"/>
       <c r="AD449" s="29"/>
     </row>
-    <row r="450" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A450" s="97" t="s">
         <v>115</v>
       </c>
@@ -29266,7 +29275,7 @@
       </c>
       <c r="AF450" s="32"/>
     </row>
-    <row r="451" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A451" s="97" t="s">
         <v>115</v>
       </c>
@@ -29310,7 +29319,7 @@
       <c r="AB451" s="9"/>
       <c r="AC451" s="9"/>
     </row>
-    <row r="452" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A452" s="97" t="s">
         <v>115</v>
       </c>
@@ -29339,7 +29348,7 @@
       <c r="AB452" s="18"/>
       <c r="AD452" s="19"/>
     </row>
-    <row r="453" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A453" s="97" t="s">
         <v>115</v>
       </c>
@@ -29368,7 +29377,7 @@
       <c r="AB453" s="18"/>
       <c r="AD453" s="19"/>
     </row>
-    <row r="454" spans="1:32" hidden="1" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A454" s="97" t="s">
         <v>115</v>
       </c>
